--- a/review_evidence_data.xlsx
+++ b/review_evidence_data.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="Rf0e02d89fe2249e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search_Strategy" sheetId="2" r:id="R68458cf4d0244e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection_Records" sheetId="3" r:id="R2d313efde9e14686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection_Flow" sheetId="4" r:id="R4feec4eeb2814ac8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Included_Studies" sheetId="5" r:id="Ra3b268c150994387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Assessment" sheetId="6" r:id="R5ca59ccd02e645e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Rubric" sheetId="7" r:id="R6ce638c48dde4b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role_Codebook" sheetId="8" r:id="R56bd0ab1f9f040be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim_Evidence" sheetId="9" r:id="R7c5cd509c0d04a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Summary" sheetId="10" r:id="Re1e82c4087714742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="R9e495aa108474b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search_Strategy" sheetId="2" r:id="R9858e7f2e84d4504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection_Records" sheetId="3" r:id="R98b2e4f6bfab40a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection_Flow" sheetId="4" r:id="R66e51ae5ed094aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Included_Studies" sheetId="5" r:id="Rd761f54ff2314a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Assessment" sheetId="6" r:id="Rb4b4e313fc5b440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Rubric" sheetId="7" r:id="R533e072addc44140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role_Codebook" sheetId="8" r:id="Rb800b5d0afa34408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim_Evidence" sheetId="9" r:id="R40340c9fbd1f4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity_Summary" sheetId="10" r:id="R2dbec79975594089"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -778,9 +778,6 @@
     <x:t xml:space="preserve">R032</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">IntelliRadar: A Comprehensive Platform to Pinpoint Malicious Packages Information from Cyber Intelligence</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">https://doi.org/10.1145/3744916.3773113; https://arxiv.org/abs/2409.15049</x:t>
   </x:si>
   <x:si>
@@ -2245,9 +2242,6 @@
     <x:t xml:space="preserve">guo2026intelliradar</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">https://doi.org/10.1145/3744916.3773113</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">IntelliRadar</x:t>
   </x:si>
   <x:si>
@@ -2257,9 +2251,6 @@
     <x:t xml:space="preserve">Software supply chain entity extraction and relation aggregation</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">ICSE 2026 listed</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">S_R033</x:t>
   </x:si>
   <x:si>
@@ -3307,9 +3298,6 @@
     <x:t xml:space="preserve">gao2026h2glm; source fields: label_ground_truth_notes, contamination_notes, ablation_detail, and reproducibility_materials</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Accepted/presented ICSE 2026 Research Track paper; the core PDF carries DOI 10.1145/3744916.3773113, but the DOI/proceedings record was not resolvable as of 2026-07-23; the official program links only the preprint</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Authoritative security databases + Multi-source confirmation + Manual validation</x:t>
   </x:si>
   <x:si>
@@ -3578,9 +3566,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">DeepSeek-V4-Flash (default for all LLM tasks); GPT-5.4-mini and Qwen-3.6-Flash evaluated as alternative backbones</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Four component-level ablations (w/o MSC: -7.85% relative F1; w/o Enrichment: -0.30%; w/o Dynamic: -3.87% relative; w/o Self-Consistency: -4.49% relative). Agent coordination not isolated from LLM reasoning. NOTE: 7.85% and 4.49% are relative percentage changes, NOT absolute percentage-point drops. Actual pp drops: 98.1-&gt;90.4 (-7.7pp) for shell detection; 98.1-&gt;93.7 (-4.4pp) for self-consistency.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Partial (benchmark P/R/F1 and real-world flagged/confirmed counts are reported; a complete population TP/FP/TN/FN matrix is not available)</x:t>
@@ -10192,14 +10177,14 @@
       <x:c r="A33" s="1" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>253</x:v>
+      <x:c r="B33" s="1" t="str">
+        <x:v>IntelliRadar: A Comprehensive Platform to Pinpoint Malicious Packages from Cyber Intelligence</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>244</x:v>
@@ -10238,16 +10223,16 @@
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="1" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>51</x:v>
@@ -10286,16 +10271,16 @@
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="1" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B35" s="1" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>51</x:v>
@@ -10334,16 +10319,16 @@
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="1" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>88</x:v>
@@ -10373,30 +10358,30 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N36" s="1" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="O36" s="1" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="O36" s="1" t="s">
+      <x:c r="P36" s="1" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="P36" s="1" t="s">
-        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="1" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2024</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
         <x:v>269</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>270</x:v>
       </x:c>
       <x:c r="F37" s="1" t="s">
         <x:v>128</x:v>
@@ -10427,25 +10412,25 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="P37" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="1" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="C38" s="1"/>
       <x:c r="D38" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F38" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G38" s="1"/>
       <x:c r="H38" s="1"/>
@@ -10461,31 +10446,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N38" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O38" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P38" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P38" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="1" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>278</x:v>
       </x:c>
       <x:c r="C39" s="1"/>
       <x:c r="D39" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F39" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G39" s="1"/>
       <x:c r="H39" s="1"/>
@@ -10501,31 +10486,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N39" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O39" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O39" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P39" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="1" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="B40" s="1" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="C40" s="1"/>
       <x:c r="D40" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F40" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G40" s="1"/>
       <x:c r="H40" s="1"/>
@@ -10544,28 +10529,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O40" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="P40" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="1" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B41" s="1" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C41" s="1"/>
       <x:c r="D41" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G41" s="1"/>
       <x:c r="H41" s="1"/>
@@ -10581,31 +10566,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N41" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O41" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P41" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P41" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="B42" s="1" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="C42" s="1"/>
       <x:c r="D42" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G42" s="1"/>
       <x:c r="H42" s="1"/>
@@ -10621,31 +10606,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N42" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O42" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O42" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P42" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="1" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="C43" s="1"/>
       <x:c r="D43" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F43" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G43" s="1"/>
       <x:c r="H43" s="1"/>
@@ -10661,31 +10646,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N43" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O43" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P43" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P43" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>296</x:v>
       </x:c>
       <x:c r="C44" s="1"/>
       <x:c r="D44" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F44" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G44" s="1"/>
       <x:c r="H44" s="1"/>
@@ -10701,31 +10686,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N44" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O44" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O44" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P44" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="1" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C45" s="1"/>
       <x:c r="D45" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G45" s="1"/>
       <x:c r="H45" s="1"/>
@@ -10741,31 +10726,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N45" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O45" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P45" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P45" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C46" s="1"/>
       <x:c r="D46" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F46" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G46" s="1"/>
       <x:c r="H46" s="1"/>
@@ -10781,31 +10766,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N46" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O46" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O46" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P46" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C47" s="1"/>
       <x:c r="D47" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F47" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G47" s="1"/>
       <x:c r="H47" s="1"/>
@@ -10821,31 +10806,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N47" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O47" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P47" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P47" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="C48" s="1"/>
       <x:c r="D48" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G48" s="1"/>
       <x:c r="H48" s="1"/>
@@ -10864,28 +10849,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O48" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="P48" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C49" s="1"/>
       <x:c r="D49" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F49" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G49" s="1"/>
       <x:c r="H49" s="1"/>
@@ -10901,31 +10886,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N49" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O49" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P49" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P49" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="1" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="C50" s="1"/>
       <x:c r="D50" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F50" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G50" s="1"/>
       <x:c r="H50" s="1"/>
@@ -10941,31 +10926,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N50" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O50" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P50" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P50" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="1" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
         <x:v>316</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>317</x:v>
       </x:c>
       <x:c r="C51" s="1"/>
       <x:c r="D51" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G51" s="1"/>
       <x:c r="H51" s="1"/>
@@ -10981,31 +10966,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N51" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O51" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O51" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P51" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="B52" s="1" t="s">
-        <x:v>320</x:v>
       </x:c>
       <x:c r="C52" s="1"/>
       <x:c r="D52" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F52" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G52" s="1"/>
       <x:c r="H52" s="1"/>
@@ -11024,28 +11009,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O52" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="P52" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="B53" s="1" t="s">
-        <x:v>323</x:v>
       </x:c>
       <x:c r="C53" s="1"/>
       <x:c r="D53" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G53" s="1"/>
       <x:c r="H53" s="1"/>
@@ -11061,31 +11046,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N53" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O53" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P53" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P53" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="1" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="B54" s="1" t="s">
-        <x:v>326</x:v>
       </x:c>
       <x:c r="C54" s="1"/>
       <x:c r="D54" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F54" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G54" s="1"/>
       <x:c r="H54" s="1"/>
@@ -11104,28 +11089,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O54" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="P54" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B55" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F55" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G55" s="1"/>
       <x:c r="H55" s="1"/>
@@ -11144,28 +11129,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O55" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="P55" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="1" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
         <x:v>331</x:v>
-      </x:c>
-      <x:c r="B56" s="1" t="s">
-        <x:v>332</x:v>
       </x:c>
       <x:c r="C56" s="1"/>
       <x:c r="D56" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G56" s="1"/>
       <x:c r="H56" s="1"/>
@@ -11181,31 +11166,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N56" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O56" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O56" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P56" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="1" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="B57" s="1" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="C57" s="1"/>
       <x:c r="D57" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F57" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G57" s="1"/>
       <x:c r="H57" s="1"/>
@@ -11221,31 +11206,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N57" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O57" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="P57" s="1" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="P57" s="1" t="s">
-        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B58" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C58" s="1"/>
       <x:c r="D58" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G58" s="1"/>
       <x:c r="H58" s="1"/>
@@ -11261,31 +11246,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N58" s="1" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="O58" s="1" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="O58" s="1" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="P58" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
       <x:c r="A59" s="1" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="B59" s="1" t="s">
-        <x:v>341</x:v>
       </x:c>
       <x:c r="C59" s="1"/>
       <x:c r="D59" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="F59" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G59" s="1"/>
       <x:c r="H59" s="1"/>
@@ -11302,7 +11287,7 @@
       </x:c>
       <x:c r="N59" s="1"/>
       <x:c r="O59" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="P59" s="1" t="s">
         <x:v>141</x:v>
@@ -11310,20 +11295,20 @@
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
       <x:c r="A60" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C60" s="1"/>
       <x:c r="D60" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G60" s="1"/>
       <x:c r="H60" s="1"/>
@@ -11340,7 +11325,7 @@
       </x:c>
       <x:c r="N60" s="1"/>
       <x:c r="O60" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="P60" s="1" t="s">
         <x:v>141</x:v>
@@ -11348,20 +11333,20 @@
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="1" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
         <x:v>346</x:v>
-      </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>347</x:v>
       </x:c>
       <x:c r="C61" s="1"/>
       <x:c r="D61" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="F61" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G61" s="1"/>
       <x:c r="H61" s="1"/>
@@ -11378,7 +11363,7 @@
       </x:c>
       <x:c r="N61" s="1"/>
       <x:c r="O61" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="P61" s="1" t="s">
         <x:v>141</x:v>
@@ -11386,20 +11371,20 @@
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="1" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
         <x:v>350</x:v>
-      </x:c>
-      <x:c r="B62" s="1" t="s">
-        <x:v>351</x:v>
       </x:c>
       <x:c r="C62" s="1"/>
       <x:c r="D62" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="F62" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G62" s="1"/>
       <x:c r="H62" s="1"/>
@@ -11416,7 +11401,7 @@
       </x:c>
       <x:c r="N62" s="1"/>
       <x:c r="O62" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="P62" s="1" t="s">
         <x:v>141</x:v>
@@ -11424,20 +11409,20 @@
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="1" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="B63" s="1" t="s">
-        <x:v>355</x:v>
       </x:c>
       <x:c r="C63" s="1"/>
       <x:c r="D63" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F63" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G63" s="1"/>
       <x:c r="H63" s="1"/>
@@ -11453,31 +11438,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N63" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O63" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P63" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
       <x:c r="A64" s="1" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
         <x:v>358</x:v>
-      </x:c>
-      <x:c r="B64" s="1" t="s">
-        <x:v>359</x:v>
       </x:c>
       <x:c r="C64" s="1"/>
       <x:c r="D64" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F64" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G64" s="1"/>
       <x:c r="H64" s="1"/>
@@ -11493,31 +11478,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N64" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O64" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P64" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
       <x:c r="A65" s="1" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
         <x:v>361</x:v>
-      </x:c>
-      <x:c r="B65" s="1" t="s">
-        <x:v>362</x:v>
       </x:c>
       <x:c r="C65" s="1"/>
       <x:c r="D65" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F65" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G65" s="1"/>
       <x:c r="H65" s="1"/>
@@ -11533,31 +11518,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N65" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O65" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P65" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
       <x:c r="A66" s="1" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="B66" s="1" t="s">
-        <x:v>366</x:v>
       </x:c>
       <x:c r="C66" s="1"/>
       <x:c r="D66" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F66" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G66" s="1"/>
       <x:c r="H66" s="1"/>
@@ -11573,31 +11558,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N66" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O66" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P66" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
       <x:c r="A67" s="1" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="B67" s="1" t="s">
-        <x:v>369</x:v>
       </x:c>
       <x:c r="C67" s="1"/>
       <x:c r="D67" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F67" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G67" s="1"/>
       <x:c r="H67" s="1"/>
@@ -11613,31 +11598,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N67" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O67" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P67" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
         <x:v>371</x:v>
-      </x:c>
-      <x:c r="B68" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
       <x:c r="C68" s="1"/>
       <x:c r="D68" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F68" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G68" s="1"/>
       <x:c r="H68" s="1"/>
@@ -11653,31 +11638,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N68" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O68" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P68" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
       <x:c r="A69" s="1" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
         <x:v>374</x:v>
-      </x:c>
-      <x:c r="B69" s="1" t="s">
-        <x:v>375</x:v>
       </x:c>
       <x:c r="C69" s="1"/>
       <x:c r="D69" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F69" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G69" s="1"/>
       <x:c r="H69" s="1"/>
@@ -11693,31 +11678,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N69" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O69" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P69" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="1" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
         <x:v>377</x:v>
-      </x:c>
-      <x:c r="B70" s="1" t="s">
-        <x:v>378</x:v>
       </x:c>
       <x:c r="C70" s="1"/>
       <x:c r="D70" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F70" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G70" s="1"/>
       <x:c r="H70" s="1"/>
@@ -11733,31 +11718,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N70" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O70" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P70" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="1" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B71" s="1" t="s">
         <x:v>380</x:v>
-      </x:c>
-      <x:c r="B71" s="1" t="s">
-        <x:v>381</x:v>
       </x:c>
       <x:c r="C71" s="1"/>
       <x:c r="D71" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F71" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G71" s="1"/>
       <x:c r="H71" s="1"/>
@@ -11773,31 +11758,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N71" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O71" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P71" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="1" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
         <x:v>383</x:v>
-      </x:c>
-      <x:c r="B72" s="1" t="s">
-        <x:v>384</x:v>
       </x:c>
       <x:c r="C72" s="1"/>
       <x:c r="D72" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F72" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G72" s="1"/>
       <x:c r="H72" s="1"/>
@@ -11813,31 +11798,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N72" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O72" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P72" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="1" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
         <x:v>386</x:v>
-      </x:c>
-      <x:c r="B73" s="1" t="s">
-        <x:v>387</x:v>
       </x:c>
       <x:c r="C73" s="1"/>
       <x:c r="D73" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F73" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G73" s="1"/>
       <x:c r="H73" s="1"/>
@@ -11853,31 +11838,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N73" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O73" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P73" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
       <x:c r="A74" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="B74" s="1" t="s">
-        <x:v>390</x:v>
       </x:c>
       <x:c r="C74" s="1"/>
       <x:c r="D74" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F74" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G74" s="1"/>
       <x:c r="H74" s="1"/>
@@ -11893,31 +11878,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N74" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O74" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P74" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
       <x:c r="A75" s="1" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
         <x:v>392</x:v>
-      </x:c>
-      <x:c r="B75" s="1" t="s">
-        <x:v>393</x:v>
       </x:c>
       <x:c r="C75" s="1"/>
       <x:c r="D75" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F75" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G75" s="1"/>
       <x:c r="H75" s="1"/>
@@ -11936,28 +11921,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O75" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="P75" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="B76" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="C76" s="1"/>
       <x:c r="D76" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F76" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G76" s="1"/>
       <x:c r="H76" s="1"/>
@@ -11973,31 +11958,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N76" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O76" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P76" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
       <x:c r="A77" s="1" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
         <x:v>399</x:v>
-      </x:c>
-      <x:c r="B77" s="1" t="s">
-        <x:v>400</x:v>
       </x:c>
       <x:c r="C77" s="1"/>
       <x:c r="D77" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F77" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G77" s="1"/>
       <x:c r="H77" s="1"/>
@@ -12013,21 +11998,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N77" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O77" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P77" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="1" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
         <x:v>402</x:v>
-      </x:c>
-      <x:c r="B78" s="1" t="s">
-        <x:v>403</x:v>
       </x:c>
       <x:c r="C78" s="1"/>
       <x:c r="D78" s="1"/>
@@ -12035,7 +12020,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F78" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G78" s="1"/>
       <x:c r="H78" s="1"/>
@@ -12051,31 +12036,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N78" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O78" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P78" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="1" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
         <x:v>405</x:v>
-      </x:c>
-      <x:c r="B79" s="1" t="s">
-        <x:v>406</x:v>
       </x:c>
       <x:c r="C79" s="1"/>
       <x:c r="D79" s="1" t="s">
-        <x:v>407</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G79" s="1"/>
       <x:c r="H79" s="1"/>
@@ -12091,31 +12076,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N79" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O79" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P79" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="1" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
         <x:v>408</x:v>
-      </x:c>
-      <x:c r="B80" s="1" t="s">
-        <x:v>409</x:v>
       </x:c>
       <x:c r="C80" s="1"/>
       <x:c r="D80" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G80" s="1"/>
       <x:c r="H80" s="1"/>
@@ -12131,21 +12116,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N80" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O80" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P80" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="1" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
         <x:v>411</x:v>
-      </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>412</x:v>
       </x:c>
       <x:c r="C81" s="1"/>
       <x:c r="D81" s="1"/>
@@ -12153,7 +12138,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F81" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G81" s="1"/>
       <x:c r="H81" s="1"/>
@@ -12169,31 +12154,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N81" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O81" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P81" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="1" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
         <x:v>413</x:v>
-      </x:c>
-      <x:c r="B82" s="1" t="s">
-        <x:v>414</x:v>
       </x:c>
       <x:c r="C82" s="1"/>
       <x:c r="D82" s="1" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G82" s="1"/>
       <x:c r="H82" s="1"/>
@@ -12209,21 +12194,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N82" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O82" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P82" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
       <x:c r="A83" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
         <x:v>416</x:v>
-      </x:c>
-      <x:c r="B83" s="1" t="s">
-        <x:v>417</x:v>
       </x:c>
       <x:c r="C83" s="1"/>
       <x:c r="D83" s="1"/>
@@ -12231,7 +12216,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F83" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G83" s="1"/>
       <x:c r="H83" s="1"/>
@@ -12247,31 +12232,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N83" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O83" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P83" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
       <x:c r="A84" s="1" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B84" s="1" t="s">
         <x:v>418</x:v>
-      </x:c>
-      <x:c r="B84" s="1" t="s">
-        <x:v>419</x:v>
       </x:c>
       <x:c r="C84" s="1"/>
       <x:c r="D84" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G84" s="1"/>
       <x:c r="H84" s="1"/>
@@ -12287,31 +12272,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N84" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O84" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P84" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
       <x:c r="A85" s="1" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="B85" s="1" t="s">
-        <x:v>422</x:v>
       </x:c>
       <x:c r="C85" s="1"/>
       <x:c r="D85" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G85" s="1"/>
       <x:c r="H85" s="1"/>
@@ -12330,18 +12315,18 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="O85" s="1" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="P85" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
       <x:c r="A86" s="1" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B86" s="1" t="s">
         <x:v>425</x:v>
-      </x:c>
-      <x:c r="B86" s="1" t="s">
-        <x:v>426</x:v>
       </x:c>
       <x:c r="C86" s="1"/>
       <x:c r="D86" s="1"/>
@@ -12349,7 +12334,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G86" s="1"/>
       <x:c r="H86" s="1"/>
@@ -12365,31 +12350,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N86" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O86" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P86" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
       <x:c r="A87" s="1" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B87" s="1" t="s">
         <x:v>427</x:v>
-      </x:c>
-      <x:c r="B87" s="1" t="s">
-        <x:v>428</x:v>
       </x:c>
       <x:c r="C87" s="1"/>
       <x:c r="D87" s="1" t="s">
-        <x:v>429</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F87" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G87" s="1"/>
       <x:c r="H87" s="1"/>
@@ -12405,21 +12390,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N87" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O87" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P87" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
       <x:c r="A88" s="1" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B88" s="1" t="s">
         <x:v>430</x:v>
-      </x:c>
-      <x:c r="B88" s="1" t="s">
-        <x:v>431</x:v>
       </x:c>
       <x:c r="C88" s="1"/>
       <x:c r="D88" s="1"/>
@@ -12427,7 +12412,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G88" s="1"/>
       <x:c r="H88" s="1"/>
@@ -12443,21 +12428,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N88" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O88" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P88" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
       <x:c r="A89" s="1" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B89" s="1" t="s">
         <x:v>432</x:v>
-      </x:c>
-      <x:c r="B89" s="1" t="s">
-        <x:v>433</x:v>
       </x:c>
       <x:c r="C89" s="1"/>
       <x:c r="D89" s="1"/>
@@ -12465,7 +12450,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F89" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G89" s="1"/>
       <x:c r="H89" s="1"/>
@@ -12481,21 +12466,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N89" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O89" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P89" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
       <x:c r="A90" s="1" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B90" s="1" t="s">
         <x:v>434</x:v>
-      </x:c>
-      <x:c r="B90" s="1" t="s">
-        <x:v>435</x:v>
       </x:c>
       <x:c r="C90" s="1"/>
       <x:c r="D90" s="1"/>
@@ -12503,7 +12488,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G90" s="1"/>
       <x:c r="H90" s="1"/>
@@ -12519,21 +12504,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N90" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O90" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P90" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
       <x:c r="A91" s="1" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B91" s="1" t="s">
         <x:v>436</x:v>
-      </x:c>
-      <x:c r="B91" s="1" t="s">
-        <x:v>437</x:v>
       </x:c>
       <x:c r="C91" s="1"/>
       <x:c r="D91" s="1"/>
@@ -12541,7 +12526,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G91" s="1"/>
       <x:c r="H91" s="1"/>
@@ -12557,21 +12542,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N91" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O91" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P91" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="1" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B92" s="1" t="s">
         <x:v>438</x:v>
-      </x:c>
-      <x:c r="B92" s="1" t="s">
-        <x:v>439</x:v>
       </x:c>
       <x:c r="C92" s="1"/>
       <x:c r="D92" s="1"/>
@@ -12579,7 +12564,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F92" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G92" s="1"/>
       <x:c r="H92" s="1"/>
@@ -12595,31 +12580,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N92" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O92" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P92" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="1" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B93" s="1" t="s">
         <x:v>440</x:v>
-      </x:c>
-      <x:c r="B93" s="1" t="s">
-        <x:v>441</x:v>
       </x:c>
       <x:c r="C93" s="1"/>
       <x:c r="D93" s="1" t="s">
-        <x:v>442</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G93" s="1"/>
       <x:c r="H93" s="1"/>
@@ -12635,21 +12620,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N93" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O93" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P93" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="1" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B94" s="1" t="s">
         <x:v>443</x:v>
-      </x:c>
-      <x:c r="B94" s="1" t="s">
-        <x:v>444</x:v>
       </x:c>
       <x:c r="C94" s="1"/>
       <x:c r="D94" s="1"/>
@@ -12657,7 +12642,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G94" s="1"/>
       <x:c r="H94" s="1"/>
@@ -12673,21 +12658,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N94" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O94" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P94" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
       <x:c r="A95" s="1" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B95" s="1" t="s">
         <x:v>445</x:v>
-      </x:c>
-      <x:c r="B95" s="1" t="s">
-        <x:v>446</x:v>
       </x:c>
       <x:c r="C95" s="1"/>
       <x:c r="D95" s="1"/>
@@ -12695,7 +12680,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F95" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G95" s="1"/>
       <x:c r="H95" s="1"/>
@@ -12711,21 +12696,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N95" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O95" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P95" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
       <x:c r="A96" s="1" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B96" s="1" t="s">
         <x:v>447</x:v>
-      </x:c>
-      <x:c r="B96" s="1" t="s">
-        <x:v>448</x:v>
       </x:c>
       <x:c r="C96" s="1"/>
       <x:c r="D96" s="1"/>
@@ -12733,7 +12718,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G96" s="1"/>
       <x:c r="H96" s="1"/>
@@ -12749,31 +12734,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N96" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O96" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P96" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="1" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
         <x:v>449</x:v>
-      </x:c>
-      <x:c r="B97" s="1" t="s">
-        <x:v>450</x:v>
       </x:c>
       <x:c r="C97" s="1"/>
       <x:c r="D97" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G97" s="1"/>
       <x:c r="H97" s="1"/>
@@ -12789,21 +12774,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N97" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O97" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P97" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="1" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B98" s="1" t="s">
         <x:v>452</x:v>
-      </x:c>
-      <x:c r="B98" s="1" t="s">
-        <x:v>453</x:v>
       </x:c>
       <x:c r="C98" s="1"/>
       <x:c r="D98" s="1"/>
@@ -12811,7 +12796,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F98" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G98" s="1"/>
       <x:c r="H98" s="1"/>
@@ -12827,21 +12812,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N98" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O98" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P98" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
       <x:c r="A99" s="1" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B99" s="1" t="s">
         <x:v>454</x:v>
-      </x:c>
-      <x:c r="B99" s="1" t="s">
-        <x:v>455</x:v>
       </x:c>
       <x:c r="C99" s="1"/>
       <x:c r="D99" s="1"/>
@@ -12849,7 +12834,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G99" s="1"/>
       <x:c r="H99" s="1"/>
@@ -12865,31 +12850,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N99" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O99" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P99" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
       <x:c r="A100" s="1" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="B100" s="1" t="s">
-        <x:v>457</x:v>
       </x:c>
       <x:c r="C100" s="1"/>
       <x:c r="D100" s="1" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G100" s="1"/>
       <x:c r="H100" s="1"/>
@@ -12905,31 +12890,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N100" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O100" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P100" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
       <x:c r="A101" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
         <x:v>459</x:v>
-      </x:c>
-      <x:c r="B101" s="1" t="s">
-        <x:v>460</x:v>
       </x:c>
       <x:c r="C101" s="1"/>
       <x:c r="D101" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F101" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G101" s="1"/>
       <x:c r="H101" s="1"/>
@@ -12945,21 +12930,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N101" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O101" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P101" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
       <x:c r="A102" s="1" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B102" s="1" t="s">
         <x:v>462</x:v>
-      </x:c>
-      <x:c r="B102" s="1" t="s">
-        <x:v>463</x:v>
       </x:c>
       <x:c r="C102" s="1"/>
       <x:c r="D102" s="1"/>
@@ -12967,7 +12952,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G102" s="1"/>
       <x:c r="H102" s="1"/>
@@ -12983,21 +12968,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N102" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O102" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P102" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
       <x:c r="A103" s="1" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
         <x:v>464</x:v>
-      </x:c>
-      <x:c r="B103" s="1" t="s">
-        <x:v>465</x:v>
       </x:c>
       <x:c r="C103" s="1"/>
       <x:c r="D103" s="1"/>
@@ -13005,7 +12990,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G103" s="1"/>
       <x:c r="H103" s="1"/>
@@ -13021,21 +13006,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N103" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O103" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P103" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
       <x:c r="A104" s="1" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
         <x:v>466</x:v>
-      </x:c>
-      <x:c r="B104" s="1" t="s">
-        <x:v>467</x:v>
       </x:c>
       <x:c r="C104" s="1"/>
       <x:c r="D104" s="1"/>
@@ -13043,7 +13028,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G104" s="1"/>
       <x:c r="H104" s="1"/>
@@ -13059,21 +13044,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N104" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O104" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P104" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
       <x:c r="A105" s="1" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B105" s="1" t="s">
         <x:v>468</x:v>
-      </x:c>
-      <x:c r="B105" s="1" t="s">
-        <x:v>469</x:v>
       </x:c>
       <x:c r="C105" s="1"/>
       <x:c r="D105" s="1"/>
@@ -13081,7 +13066,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G105" s="1"/>
       <x:c r="H105" s="1"/>
@@ -13097,31 +13082,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N105" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O105" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P105" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
       <x:c r="A106" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B106" s="1" t="s">
         <x:v>470</x:v>
-      </x:c>
-      <x:c r="B106" s="1" t="s">
-        <x:v>471</x:v>
       </x:c>
       <x:c r="C106" s="1"/>
       <x:c r="D106" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G106" s="1"/>
       <x:c r="H106" s="1"/>
@@ -13137,31 +13122,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N106" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O106" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P106" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
       <x:c r="A107" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B107" s="1" t="s">
         <x:v>473</x:v>
-      </x:c>
-      <x:c r="B107" s="1" t="s">
-        <x:v>474</x:v>
       </x:c>
       <x:c r="C107" s="1"/>
       <x:c r="D107" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G107" s="1"/>
       <x:c r="H107" s="1"/>
@@ -13177,21 +13162,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N107" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O107" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P107" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
       <x:c r="A108" s="1" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B108" s="1" t="s">
         <x:v>476</x:v>
-      </x:c>
-      <x:c r="B108" s="1" t="s">
-        <x:v>477</x:v>
       </x:c>
       <x:c r="C108" s="1"/>
       <x:c r="D108" s="1"/>
@@ -13199,7 +13184,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G108" s="1"/>
       <x:c r="H108" s="1"/>
@@ -13215,31 +13200,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N108" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O108" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P108" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
       <x:c r="A109" s="1" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B109" s="1" t="s">
         <x:v>478</x:v>
-      </x:c>
-      <x:c r="B109" s="1" t="s">
-        <x:v>479</x:v>
       </x:c>
       <x:c r="C109" s="1"/>
       <x:c r="D109" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G109" s="1"/>
       <x:c r="H109" s="1"/>
@@ -13255,21 +13240,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N109" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O109" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P109" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="42" customHeight="1">
       <x:c r="A110" s="1" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B110" s="1" t="s">
         <x:v>481</x:v>
-      </x:c>
-      <x:c r="B110" s="1" t="s">
-        <x:v>482</x:v>
       </x:c>
       <x:c r="C110" s="1"/>
       <x:c r="D110" s="1"/>
@@ -13277,7 +13262,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G110" s="1"/>
       <x:c r="H110" s="1"/>
@@ -13293,31 +13278,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N110" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O110" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P110" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
       <x:c r="A111" s="1" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B111" s="1" t="s">
         <x:v>483</x:v>
-      </x:c>
-      <x:c r="B111" s="1" t="s">
-        <x:v>484</x:v>
       </x:c>
       <x:c r="C111" s="1"/>
       <x:c r="D111" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G111" s="1"/>
       <x:c r="H111" s="1"/>
@@ -13336,18 +13321,18 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O111" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="P111" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="42" customHeight="1">
       <x:c r="A112" s="1" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B112" s="1" t="s">
         <x:v>486</x:v>
-      </x:c>
-      <x:c r="B112" s="1" t="s">
-        <x:v>487</x:v>
       </x:c>
       <x:c r="C112" s="1"/>
       <x:c r="D112" s="1"/>
@@ -13355,7 +13340,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G112" s="1"/>
       <x:c r="H112" s="1"/>
@@ -13371,21 +13356,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N112" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O112" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P112" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="42" customHeight="1">
       <x:c r="A113" s="1" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B113" s="1" t="s">
         <x:v>488</x:v>
-      </x:c>
-      <x:c r="B113" s="1" t="s">
-        <x:v>489</x:v>
       </x:c>
       <x:c r="C113" s="1"/>
       <x:c r="D113" s="1"/>
@@ -13393,7 +13378,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G113" s="1"/>
       <x:c r="H113" s="1"/>
@@ -13409,31 +13394,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N113" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O113" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P113" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="42" customHeight="1">
       <x:c r="A114" s="1" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="B114" s="1" t="s">
         <x:v>490</x:v>
-      </x:c>
-      <x:c r="B114" s="1" t="s">
-        <x:v>491</x:v>
       </x:c>
       <x:c r="C114" s="1"/>
       <x:c r="D114" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G114" s="1"/>
       <x:c r="H114" s="1"/>
@@ -13452,28 +13437,28 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="O114" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="P114" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="42" customHeight="1">
       <x:c r="A115" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B115" s="1" t="s">
         <x:v>493</x:v>
-      </x:c>
-      <x:c r="B115" s="1" t="s">
-        <x:v>494</x:v>
       </x:c>
       <x:c r="C115" s="1"/>
       <x:c r="D115" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="E115" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G115" s="1"/>
       <x:c r="H115" s="1"/>
@@ -13489,21 +13474,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N115" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O115" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="P115" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="42" customHeight="1">
       <x:c r="A116" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B116" s="1" t="s">
         <x:v>496</x:v>
-      </x:c>
-      <x:c r="B116" s="1" t="s">
-        <x:v>497</x:v>
       </x:c>
       <x:c r="C116" s="1"/>
       <x:c r="D116" s="1"/>
@@ -13511,7 +13496,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G116" s="1"/>
       <x:c r="H116" s="1"/>
@@ -13527,21 +13512,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N116" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O116" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P116" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="42" customHeight="1">
       <x:c r="A117" s="1" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B117" s="1" t="s">
         <x:v>498</x:v>
-      </x:c>
-      <x:c r="B117" s="1" t="s">
-        <x:v>499</x:v>
       </x:c>
       <x:c r="C117" s="1"/>
       <x:c r="D117" s="1"/>
@@ -13549,7 +13534,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G117" s="1"/>
       <x:c r="H117" s="1"/>
@@ -13565,21 +13550,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N117" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O117" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P117" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="42" customHeight="1">
       <x:c r="A118" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B118" s="1" t="s">
         <x:v>500</x:v>
-      </x:c>
-      <x:c r="B118" s="1" t="s">
-        <x:v>501</x:v>
       </x:c>
       <x:c r="C118" s="1"/>
       <x:c r="D118" s="1"/>
@@ -13587,7 +13572,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G118" s="1"/>
       <x:c r="H118" s="1"/>
@@ -13603,21 +13588,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N118" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O118" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P118" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="42" customHeight="1">
       <x:c r="A119" s="1" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B119" s="1" t="s">
         <x:v>502</x:v>
-      </x:c>
-      <x:c r="B119" s="1" t="s">
-        <x:v>503</x:v>
       </x:c>
       <x:c r="C119" s="1"/>
       <x:c r="D119" s="1"/>
@@ -13625,7 +13610,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G119" s="1"/>
       <x:c r="H119" s="1"/>
@@ -13641,21 +13626,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N119" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O119" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P119" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="42" customHeight="1">
       <x:c r="A120" s="1" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B120" s="1" t="s">
         <x:v>504</x:v>
-      </x:c>
-      <x:c r="B120" s="1" t="s">
-        <x:v>505</x:v>
       </x:c>
       <x:c r="C120" s="1"/>
       <x:c r="D120" s="1"/>
@@ -13663,7 +13648,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F120" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G120" s="1"/>
       <x:c r="H120" s="1"/>
@@ -13679,21 +13664,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N120" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O120" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P120" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="42" customHeight="1">
       <x:c r="A121" s="1" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B121" s="1" t="s">
         <x:v>506</x:v>
-      </x:c>
-      <x:c r="B121" s="1" t="s">
-        <x:v>507</x:v>
       </x:c>
       <x:c r="C121" s="1"/>
       <x:c r="D121" s="1"/>
@@ -13701,7 +13686,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F121" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G121" s="1"/>
       <x:c r="H121" s="1"/>
@@ -13717,21 +13702,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N121" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O121" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P121" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="42" customHeight="1">
       <x:c r="A122" s="1" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B122" s="1" t="s">
         <x:v>508</x:v>
-      </x:c>
-      <x:c r="B122" s="1" t="s">
-        <x:v>509</x:v>
       </x:c>
       <x:c r="C122" s="1"/>
       <x:c r="D122" s="1"/>
@@ -13739,7 +13724,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G122" s="1"/>
       <x:c r="H122" s="1"/>
@@ -13755,31 +13740,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N122" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O122" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P122" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="42" customHeight="1">
       <x:c r="A123" s="1" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B123" s="1" t="s">
         <x:v>510</x:v>
-      </x:c>
-      <x:c r="B123" s="1" t="s">
-        <x:v>511</x:v>
       </x:c>
       <x:c r="C123" s="1"/>
       <x:c r="D123" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="E123" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F123" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G123" s="1"/>
       <x:c r="H123" s="1"/>
@@ -13795,21 +13780,21 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N123" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O123" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P123" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="42" customHeight="1">
       <x:c r="A124" s="1" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B124" s="1" t="s">
         <x:v>513</x:v>
-      </x:c>
-      <x:c r="B124" s="1" t="s">
-        <x:v>514</x:v>
       </x:c>
       <x:c r="C124" s="1"/>
       <x:c r="D124" s="1"/>
@@ -13817,7 +13802,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="F124" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G124" s="1"/>
       <x:c r="H124" s="1"/>
@@ -13833,31 +13818,31 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N124" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O124" s="1" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="P124" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="42" customHeight="1">
       <x:c r="A125" s="1" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B125" s="1" t="s">
         <x:v>515</x:v>
-      </x:c>
-      <x:c r="B125" s="1" t="s">
-        <x:v>516</x:v>
       </x:c>
       <x:c r="C125" s="1"/>
       <x:c r="D125" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="E125" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="F125" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G125" s="1"/>
       <x:c r="H125" s="1"/>
@@ -13873,27 +13858,27 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="N125" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="O125" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="P125" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="42" customHeight="1">
       <x:c r="A126" s="1" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B126" s="1" t="s">
         <x:v>518</x:v>
-      </x:c>
-      <x:c r="B126" s="1" t="s">
-        <x:v>519</x:v>
       </x:c>
       <x:c r="C126" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="D126" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E126" s="1" t="s">
         <x:v>105</x:v>
@@ -13924,24 +13909,24 @@
       </x:c>
       <x:c r="N126" s="1"/>
       <x:c r="O126" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="P126" s="1" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="P126" s="1" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="42" customHeight="1">
       <x:c r="A127" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B127" s="1" t="s">
         <x:v>523</x:v>
-      </x:c>
-      <x:c r="B127" s="1" t="s">
-        <x:v>524</x:v>
       </x:c>
       <x:c r="C127" s="1">
         <x:v>2027</x:v>
       </x:c>
       <x:c r="D127" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="E127" s="1" t="s">
         <x:v>101</x:v>
@@ -13972,24 +13957,24 @@
       </x:c>
       <x:c r="N127" s="1"/>
       <x:c r="O127" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="P127" s="1" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="P127" s="1" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="42" customHeight="1">
       <x:c r="A128" s="1" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B128" s="1" t="s">
         <x:v>526</x:v>
-      </x:c>
-      <x:c r="B128" s="1" t="s">
-        <x:v>527</x:v>
       </x:c>
       <x:c r="C128" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="D128" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="E128" s="1" t="s">
         <x:v>101</x:v>
@@ -14020,10 +14005,10 @@
       </x:c>
       <x:c r="N128" s="1"/>
       <x:c r="O128" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="P128" s="1" t="s">
         <x:v>521</x:v>
-      </x:c>
-      <x:c r="P128" s="1" t="s">
-        <x:v>522</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14042,24 +14027,24 @@
   <x:sheetData>
     <x:row r="1" ht="32.099998474121094" customHeight="1">
       <x:c r="A1" s="2" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
+      <x:c r="C1" s="2" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
+      <x:c r="D1" s="2" t="s">
         <x:v>531</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="E1" s="2" t="s">
         <x:v>532</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33.95000076293945" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>534</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>62</x:v>
@@ -14073,12 +14058,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>535</x:v>
+        <x:v>534</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="33.95000076293945" customHeight="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>536</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>22</x:v>
@@ -14092,12 +14077,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>537</x:v>
+        <x:v>536</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="33.95000076293945" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>538</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>154</x:v>
@@ -14111,12 +14096,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="33.95000076293945" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>540</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>238</x:v>
@@ -14130,12 +14115,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>541</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33.95000076293945" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>111</x:v>
@@ -14149,12 +14134,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33.95000076293945" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>127</x:v>
@@ -14168,12 +14153,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>545</x:v>
+        <x:v>544</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33.95000076293945" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>546</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>88</x:v>
@@ -14187,12 +14172,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>546</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33.95000076293945" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>548</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>39</x:v>
@@ -14206,12 +14191,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>548</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33.95000076293945" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>38</x:v>
@@ -14225,12 +14210,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="33.95000076293945" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>552</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2</x:v>
@@ -14244,12 +14229,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="33.95000076293945" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>36</x:v>
@@ -14263,12 +14248,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="33.95000076293945" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>4</x:v>
@@ -14282,12 +14267,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="33.95000076293945" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>32</x:v>
@@ -14301,12 +14286,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="33.95000076293945" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>32</x:v>
@@ -14320,12 +14305,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="33.95000076293945" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>30</x:v>
@@ -14338,12 +14323,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="33.95000076293945" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>13</x:v>
@@ -14357,12 +14342,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>564</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33.95000076293945" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>14</x:v>
@@ -14376,12 +14361,12 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>566</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="33.95000076293945" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>5</x:v>
@@ -14395,7 +14380,7 @@
         <x:v>OK</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>568</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14424,49 +14409,49 @@
   <x:sheetData>
     <x:row r="1" ht="32.099998474121094" customHeight="1">
       <x:c r="A1" s="2" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
+      <x:c r="C1" s="2" t="s">
         <x:v>571</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>572</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>573</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="G1" s="2" t="s">
         <x:v>574</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>575</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>576</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>577</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>578</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>579</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>580</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>581</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>582</x:v>
-      </x:c>
-      <x:c r="O1" s="2" t="s">
-        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="54.95000076293945" customHeight="1">
@@ -14474,41 +14459,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>584</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>587</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="G2" s="1" t="s">
         <x:v>588</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>589</x:v>
       </x:c>
       <x:c r="H2" s="1"/>
       <x:c r="I2" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="K2" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="L2" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="M2" s="1" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="M2" s="1" t="s">
+      <x:c r="N2" s="1" t="s">
         <x:v>594</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>595</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
         <x:v>129</x:v>
@@ -14519,41 +14504,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>596</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>597</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>598</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>599</x:v>
-      </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H3" s="1"/>
       <x:c r="I3" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J3" s="1" t="s">
+      <x:c r="K3" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>592</x:v>
-      </x:c>
       <x:c r="L3" s="1" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="M3" s="1" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="M3" s="1" t="s">
+      <x:c r="N3" s="1" t="s">
         <x:v>601</x:v>
-      </x:c>
-      <x:c r="N3" s="1" t="s">
-        <x:v>602</x:v>
       </x:c>
       <x:c r="O3" s="1" t="s">
         <x:v>212</x:v>
@@ -14564,41 +14549,41 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>603</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>604</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>605</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
+      <x:c r="F4" s="1" t="s">
         <x:v>606</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>607</x:v>
-      </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="J4" s="1" t="s">
+      <x:c r="K4" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K4" s="1" t="s">
+      <x:c r="L4" s="1" t="s">
         <x:v>610</x:v>
       </x:c>
-      <x:c r="L4" s="1" t="s">
+      <x:c r="M4" s="1" t="s">
         <x:v>611</x:v>
       </x:c>
-      <x:c r="M4" s="1" t="s">
+      <x:c r="N4" s="1" t="s">
         <x:v>612</x:v>
-      </x:c>
-      <x:c r="N4" s="1" t="s">
-        <x:v>613</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
         <x:v>212</x:v>
@@ -14609,41 +14594,41 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>615</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>618</x:v>
-      </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
       <x:c r="I5" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J5" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J5" s="1" t="s">
+      <x:c r="K5" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K5" s="1" t="s">
+      <x:c r="L5" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L5" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
       <x:c r="M5" s="1" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="N5" s="1" t="s">
         <x:v>619</x:v>
-      </x:c>
-      <x:c r="N5" s="1" t="s">
-        <x:v>620</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
         <x:v>212</x:v>
@@ -14654,41 +14639,41 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>621</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>622</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>623</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
         <x:v>624</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>625</x:v>
-      </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H6" s="1"/>
       <x:c r="I6" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="K6" s="1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="L6" s="1" t="s">
         <x:v>626</x:v>
       </x:c>
-      <x:c r="K6" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="L6" s="1" t="s">
+      <x:c r="M6" s="1" t="s">
         <x:v>627</x:v>
       </x:c>
-      <x:c r="M6" s="1" t="s">
+      <x:c r="N6" s="1" t="s">
         <x:v>628</x:v>
-      </x:c>
-      <x:c r="N6" s="1" t="s">
-        <x:v>629</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
         <x:v>212</x:v>
@@ -14699,41 +14684,41 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>631</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
         <x:v>632</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>633</x:v>
-      </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H7" s="1"/>
       <x:c r="I7" s="1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="J7" s="1" t="s">
+      <x:c r="K7" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K7" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
       <x:c r="L7" s="1" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="M7" s="1" t="s">
         <x:v>634</x:v>
       </x:c>
-      <x:c r="M7" s="1" t="s">
+      <x:c r="N7" s="1" t="s">
         <x:v>635</x:v>
-      </x:c>
-      <x:c r="N7" s="1" t="s">
-        <x:v>636</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
         <x:v>212</x:v>
@@ -14744,43 +14729,43 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>637</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>638</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>639</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="s">
+      <x:c r="G8" s="1" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
         <x:v>640</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="s">
+      <x:c r="I8" s="1" t="s">
         <x:v>589</x:v>
       </x:c>
-      <x:c r="H8" s="1" t="s">
+      <x:c r="J8" s="1" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="K8" s="1" t="s">
         <x:v>641</x:v>
       </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="K8" s="1" t="s">
+      <x:c r="L8" s="1" t="s">
         <x:v>642</x:v>
       </x:c>
-      <x:c r="L8" s="1" t="s">
+      <x:c r="M8" s="1" t="s">
         <x:v>643</x:v>
       </x:c>
-      <x:c r="M8" s="1" t="s">
+      <x:c r="N8" s="1" t="s">
         <x:v>644</x:v>
-      </x:c>
-      <x:c r="N8" s="1" t="s">
-        <x:v>645</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
         <x:v>212</x:v>
@@ -14791,41 +14776,41 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>646</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>647</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>648</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>649</x:v>
-      </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H9" s="1"/>
       <x:c r="I9" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J9" s="1" t="s">
+      <x:c r="K9" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K9" s="1" t="s">
-        <x:v>592</x:v>
-      </x:c>
       <x:c r="L9" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="M9" s="1" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="N9" s="1" t="s">
         <x:v>650</x:v>
-      </x:c>
-      <x:c r="N9" s="1" t="s">
-        <x:v>651</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
         <x:v>212</x:v>
@@ -14836,41 +14821,41 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>652</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>653</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>654</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
+      <x:c r="F10" s="1" t="s">
         <x:v>655</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>656</x:v>
-      </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H10" s="1"/>
       <x:c r="I10" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L10" s="1" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="M10" s="1" t="s">
         <x:v>657</x:v>
       </x:c>
-      <x:c r="M10" s="1" t="s">
+      <x:c r="N10" s="1" t="s">
         <x:v>658</x:v>
-      </x:c>
-      <x:c r="N10" s="1" t="s">
-        <x:v>659</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
         <x:v>129</x:v>
@@ -14881,43 +14866,43 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>661</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
         <x:v>662</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="F11" s="1" t="s">
         <x:v>663</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
+      <x:c r="G11" s="1" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="H11" s="1" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="I11" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J11" s="1" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="K11" s="1" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="L11" s="1" t="s">
         <x:v>664</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="H11" s="1" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="K11" s="1" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="L11" s="1" t="s">
+      <x:c r="M11" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="N11" s="1" t="s">
         <x:v>665</x:v>
-      </x:c>
-      <x:c r="M11" s="1" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="N11" s="1" t="s">
-        <x:v>666</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
         <x:v>212</x:v>
@@ -14928,41 +14913,41 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>667</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>668</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
         <x:v>669</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>670</x:v>
-      </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>656</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="H12" s="1"/>
       <x:c r="I12" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="K12" s="1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="L12" s="1" t="s">
         <x:v>671</x:v>
       </x:c>
-      <x:c r="K12" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="L12" s="1" t="s">
+      <x:c r="M12" s="1" t="s">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="M12" s="1" t="s">
+      <x:c r="N12" s="1" t="s">
         <x:v>673</x:v>
-      </x:c>
-      <x:c r="N12" s="1" t="s">
-        <x:v>674</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
         <x:v>212</x:v>
@@ -14973,43 +14958,43 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>675</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>676</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
         <x:v>677</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="F13" s="1" t="s">
         <x:v>678</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="K13" s="1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="L13" s="1" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="M13" s="1" t="s">
         <x:v>679</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="K13" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="L13" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="M13" s="1" t="s">
+      <x:c r="N13" s="1" t="s">
         <x:v>680</x:v>
-      </x:c>
-      <x:c r="N13" s="1" t="s">
-        <x:v>681</x:v>
       </x:c>
       <x:c r="O13" s="1" t="s">
         <x:v>129</x:v>
@@ -15020,41 +15005,41 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>682</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>683</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>684</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
         <x:v>685</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>686</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H14" s="1"/>
       <x:c r="I14" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J14" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L14" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="N14" s="1" t="s">
         <x:v>687</x:v>
-      </x:c>
-      <x:c r="N14" s="1" t="s">
-        <x:v>688</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
         <x:v>212</x:v>
@@ -15065,43 +15050,43 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>689</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>690</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
         <x:v>691</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
+      <x:c r="F15" s="1" t="s">
         <x:v>692</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>693</x:v>
-      </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
         <x:v>589</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>590</x:v>
       </x:c>
       <x:c r="J15" s="1" t="str">
         <x:v>Peer-reviewed publication</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="L15" s="1" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="M15" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="N15" s="1" t="s">
         <x:v>694</x:v>
-      </x:c>
-      <x:c r="M15" s="1" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="N15" s="1" t="s">
-        <x:v>695</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
         <x:v>129</x:v>
@@ -15112,41 +15097,41 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>696</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>697</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>174</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>698</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>699</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H16" s="1"/>
       <x:c r="I16" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J16" s="1" t="s">
+      <x:c r="K16" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K16" s="1" t="s">
+      <x:c r="L16" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L16" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
       <x:c r="M16" s="1" t="s">
-        <x:v>687</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="N16" s="1" t="s">
-        <x:v>700</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
         <x:v>212</x:v>
@@ -15157,41 +15142,41 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>701</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>702</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>177</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>703</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>704</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H17" s="1"/>
       <x:c r="I17" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J17" s="1" t="s">
+      <x:c r="K17" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K17" s="1" t="s">
+      <x:c r="L17" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L17" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
       <x:c r="M17" s="1" t="s">
+        <x:v>704</x:v>
+      </x:c>
+      <x:c r="N17" s="1" t="s">
         <x:v>705</x:v>
-      </x:c>
-      <x:c r="N17" s="1" t="s">
-        <x:v>706</x:v>
       </x:c>
       <x:c r="O17" s="1" t="s">
         <x:v>212</x:v>
@@ -15202,41 +15187,41 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>707</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>708</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>709</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
+      <x:c r="F18" s="1" t="s">
         <x:v>710</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>711</x:v>
-      </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H18" s="1"/>
       <x:c r="I18" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J18" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L18" s="1" t="s">
+        <x:v>711</x:v>
+      </x:c>
+      <x:c r="M18" s="1" t="s">
         <x:v>712</x:v>
       </x:c>
-      <x:c r="M18" s="1" t="s">
+      <x:c r="N18" s="1" t="s">
         <x:v>713</x:v>
-      </x:c>
-      <x:c r="N18" s="1" t="s">
-        <x:v>714</x:v>
       </x:c>
       <x:c r="O18" s="1" t="s">
         <x:v>129</x:v>
@@ -15247,41 +15232,41 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>715</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>716</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>717</x:v>
       </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>718</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H19" s="1"/>
       <x:c r="I19" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J19" s="1" t="s">
+      <x:c r="K19" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K19" s="1" t="s">
-        <x:v>592</x:v>
-      </x:c>
       <x:c r="L19" s="1" t="s">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="M19" s="1" t="s">
         <x:v>719</x:v>
       </x:c>
-      <x:c r="M19" s="1" t="s">
+      <x:c r="N19" s="1" t="s">
         <x:v>720</x:v>
-      </x:c>
-      <x:c r="N19" s="1" t="s">
-        <x:v>721</x:v>
       </x:c>
       <x:c r="O19" s="1" t="s">
         <x:v>212</x:v>
@@ -15292,41 +15277,41 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>722</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>723</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
         <x:v>189</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>724</x:v>
       </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>725</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H20" s="1"/>
       <x:c r="I20" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="K20" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K20" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
       <x:c r="L20" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="M20" s="1" t="s">
-        <x:v>687</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="N20" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="O20" s="1" t="s">
         <x:v>212</x:v>
@@ -15337,41 +15322,41 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>727</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>728</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
         <x:v>233</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
+        <x:v>728</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>729</x:v>
       </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>730</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H21" s="1"/>
       <x:c r="I21" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J21" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K21" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L21" s="1" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="M21" s="1" t="s">
         <x:v>731</x:v>
       </x:c>
-      <x:c r="M21" s="1" t="s">
+      <x:c r="N21" s="1" t="s">
         <x:v>732</x:v>
-      </x:c>
-      <x:c r="N21" s="1" t="s">
-        <x:v>733</x:v>
       </x:c>
       <x:c r="O21" s="1" t="s">
         <x:v>212</x:v>
@@ -15382,41 +15367,41 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>734</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>735</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>736</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="F22" s="1" t="s">
         <x:v>737</x:v>
       </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>738</x:v>
-      </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H22" s="1"/>
       <x:c r="I22" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="K22" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K22" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
       <x:c r="L22" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="M22" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="N22" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="O22" s="1" t="s">
         <x:v>212</x:v>
@@ -15427,41 +15412,41 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>740</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="str">
+        <x:v>https://doi.org/10.1145/3744916.3773113</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
         <x:v>741</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="F23" s="1" t="s">
         <x:v>742</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>743</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>744</x:v>
-      </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H23" s="1"/>
       <x:c r="I23" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="str">
+        <x:v>Peer-reviewed publication</x:v>
       </x:c>
       <x:c r="K23" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="L23" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="M23" s="1" t="s">
-        <x:v>745</x:v>
-      </x:c>
-      <x:c r="N23" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>743</x:v>
+      </x:c>
+      <x:c r="N23" s="1" t="str">
+        <x:v>ICSE 2026</x:v>
       </x:c>
       <x:c r="O23" s="1" t="s">
         <x:v>212</x:v>
@@ -15472,41 +15457,41 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
         <x:v>747</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="F24" s="1" t="s">
         <x:v>748</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>749</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>751</x:v>
-      </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H24" s="1"/>
       <x:c r="I24" s="1" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="J24" s="1" t="s">
-        <x:v>609</x:v>
-      </x:c>
       <x:c r="K24" s="1" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="L24" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L24" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
       <x:c r="M24" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="N24" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="O24" s="1" t="s">
         <x:v>212</x:v>
@@ -15517,41 +15502,41 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>753</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="F25" s="1" t="s">
         <x:v>754</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>755</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>756</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>757</x:v>
-      </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H25" s="1"/>
       <x:c r="I25" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="K25" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K25" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
       <x:c r="L25" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="M25" s="1" t="s">
-        <x:v>758</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="N25" s="1" t="s">
-        <x:v>759</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="O25" s="1" t="s">
         <x:v>212</x:v>
@@ -15562,41 +15547,41 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="F26" s="1" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="G26" s="1" t="s">
         <x:v>762</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>763</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>764</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>765</x:v>
       </x:c>
       <x:c r="H26" s="1"/>
       <x:c r="I26" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J26" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K26" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L26" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="M26" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="N26" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="O26" s="1" t="s">
         <x:v>129</x:v>
@@ -15607,41 +15592,41 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>769</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="F27" s="1" t="s">
         <x:v>770</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>771</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>772</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>773</x:v>
-      </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H27" s="1"/>
       <x:c r="I27" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="K27" s="1" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="K27" s="1" t="s">
-        <x:v>610</x:v>
-      </x:c>
       <x:c r="L27" s="1" t="s">
-        <x:v>694</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="M27" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N27" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="O27" s="1" t="s">
         <x:v>212</x:v>
@@ -15652,41 +15637,41 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
         <x:v>775</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>777</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>778</x:v>
-      </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>656</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H28" s="1"/>
       <x:c r="I28" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J28" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K28" s="1" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="L28" s="1" t="s">
         <x:v>610</x:v>
       </x:c>
-      <x:c r="L28" s="1" t="s">
-        <x:v>611</x:v>
-      </x:c>
       <x:c r="M28" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="N28" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="O28" s="1" t="s">
         <x:v>129</x:v>
@@ -15697,41 +15682,41 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>219</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H29" s="1"/>
       <x:c r="I29" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J29" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K29" s="1" t="s">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="L29" s="1" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="M29" s="1" t="s">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="N29" s="1" t="s">
         <x:v>785</x:v>
-      </x:c>
-      <x:c r="L29" s="1" t="s">
-        <x:v>786</x:v>
-      </x:c>
-      <x:c r="M29" s="1" t="s">
-        <x:v>787</x:v>
-      </x:c>
-      <x:c r="N29" s="1" t="s">
-        <x:v>788</x:v>
       </x:c>
       <x:c r="O29" s="1" t="s">
         <x:v>212</x:v>
@@ -15742,41 +15727,41 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>789</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
+      <x:c r="F30" s="1" t="s">
         <x:v>790</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>791</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>792</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>793</x:v>
-      </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H30" s="1"/>
       <x:c r="I30" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="K30" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="L30" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="M30" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="N30" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="O30" s="1" t="s">
         <x:v>212</x:v>
@@ -15787,43 +15772,43 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>794</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>796</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="G31" s="1" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="I31" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="K31" s="1" t="s">
         <x:v>797</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
+      <x:c r="L31" s="1" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="M31" s="1" t="s">
         <x:v>798</x:v>
       </x:c>
-      <x:c r="F31" s="1" t="s">
+      <x:c r="N31" s="1" t="s">
         <x:v>799</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="H31" s="1" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="I31" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="J31" s="1" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="K31" s="1" t="s">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="L31" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="M31" s="1" t="s">
-        <x:v>801</x:v>
-      </x:c>
-      <x:c r="N31" s="1" t="s">
-        <x:v>802</x:v>
       </x:c>
       <x:c r="O31" s="1" t="s">
         <x:v>212</x:v>
@@ -15834,41 +15819,41 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>801</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>802</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
         <x:v>803</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>804</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>805</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>806</x:v>
-      </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H32" s="1"/>
       <x:c r="I32" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J32" s="1" t="s">
-        <x:v>591</x:v>
-      </x:c>
       <x:c r="K32" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="L32" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="M32" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="N32" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="O32" s="1" t="s">
         <x:v>212</x:v>
@@ -15879,41 +15864,41 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>806</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>809</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>810</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>811</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>812</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="H33" s="1"/>
       <x:c r="I33" s="1" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="J33" s="1" t="s">
+      <x:c r="K33" s="1" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="K33" s="1" t="s">
+      <x:c r="L33" s="1" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="L33" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
       <x:c r="M33" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="N33" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="O33" s="1" t="s">
         <x:v>212</x:v>
@@ -15957,153 +15942,153 @@
   <x:sheetData>
     <x:row r="1" ht="32.099998474121094" customHeight="1">
       <x:c r="A1" s="2" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
         <x:v>571</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>572</x:v>
-      </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>815</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
         <x:v>816</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
+      <x:c r="I1" s="2" t="s">
         <x:v>817</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="J1" s="2" t="s">
         <x:v>818</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
+      <x:c r="K1" s="2" t="s">
         <x:v>819</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
+      <x:c r="L1" s="2" t="s">
         <x:v>820</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="s">
+      <x:c r="M1" s="2" t="s">
         <x:v>821</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="s">
+      <x:c r="N1" s="2" t="s">
         <x:v>822</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="s">
+      <x:c r="O1" s="2" t="s">
         <x:v>823</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="s">
+      <x:c r="P1" s="2" t="s">
         <x:v>824</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="s">
+      <x:c r="Q1" s="2" t="s">
         <x:v>825</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="s">
+      <x:c r="R1" s="2" t="s">
         <x:v>826</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="s">
+      <x:c r="S1" s="2" t="s">
         <x:v>827</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="s">
+      <x:c r="T1" s="2" t="s">
         <x:v>828</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="s">
+      <x:c r="U1" s="2" t="s">
         <x:v>829</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="s">
+      <x:c r="V1" s="2" t="s">
         <x:v>830</x:v>
       </x:c>
-      <x:c r="T1" s="2" t="s">
+      <x:c r="W1" s="2" t="s">
         <x:v>831</x:v>
       </x:c>
-      <x:c r="U1" s="2" t="s">
+      <x:c r="X1" s="2" t="s">
         <x:v>832</x:v>
       </x:c>
-      <x:c r="V1" s="2" t="s">
+      <x:c r="Y1" s="2" t="s">
         <x:v>833</x:v>
       </x:c>
-      <x:c r="W1" s="2" t="s">
+      <x:c r="Z1" s="2" t="s">
         <x:v>834</x:v>
       </x:c>
-      <x:c r="X1" s="2" t="s">
+      <x:c r="AA1" s="2" t="s">
         <x:v>835</x:v>
       </x:c>
-      <x:c r="Y1" s="2" t="s">
+      <x:c r="AB1" s="2" t="s">
         <x:v>836</x:v>
       </x:c>
-      <x:c r="Z1" s="2" t="s">
+      <x:c r="AC1" s="2" t="s">
         <x:v>837</x:v>
       </x:c>
-      <x:c r="AA1" s="2" t="s">
+      <x:c r="AD1" s="2" t="s">
         <x:v>838</x:v>
-      </x:c>
-      <x:c r="AB1" s="2" t="s">
-        <x:v>839</x:v>
-      </x:c>
-      <x:c r="AC1" s="2" t="s">
-        <x:v>840</x:v>
-      </x:c>
-      <x:c r="AD1" s="2" t="s">
-        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="87.94999694824219" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>584</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>585</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
         <x:v>842</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="H2" s="1" t="s">
         <x:v>843</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="I2" s="1" t="s">
         <x:v>844</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="J2" s="1" t="s">
         <x:v>845</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="K2" s="1" t="s">
         <x:v>846</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="L2" s="1" t="s">
         <x:v>847</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="M2" s="1" t="s">
         <x:v>848</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="N2" s="1" t="s">
         <x:v>849</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="O2" s="1" t="s">
         <x:v>850</x:v>
       </x:c>
-      <x:c r="M2" s="1" t="s">
+      <x:c r="P2" s="1" t="s">
         <x:v>851</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>852</x:v>
-      </x:c>
-      <x:c r="O2" s="1" t="s">
-        <x:v>853</x:v>
-      </x:c>
-      <x:c r="P2" s="1" t="s">
-        <x:v>854</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R2" s="1" t="s">
-        <x:v>855</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="S2" s="1" t="s">
-        <x:v>856</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="T2" s="1">
         <x:v>1</x:v>
@@ -16127,75 +16112,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA2" s="1" t="s">
-        <x:v>857</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="AB2" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC2" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD2" s="1" t="s">
-        <x:v>859</x:v>
+        <x:v>856</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="87.94999694824219" customHeight="1">
       <x:c r="A3" s="1" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>596</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>597</x:v>
-      </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>860</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>861</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="H3" s="1" t="s">
         <x:v>862</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="I3" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
         <x:v>863</x:v>
       </x:c>
-      <x:c r="G3" s="1" t="s">
+      <x:c r="K3" s="1" t="s">
         <x:v>864</x:v>
       </x:c>
-      <x:c r="H3" s="1" t="s">
+      <x:c r="L3" s="1" t="s">
         <x:v>865</x:v>
       </x:c>
-      <x:c r="I3" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="s">
+      <x:c r="M3" s="1" t="s">
         <x:v>866</x:v>
       </x:c>
-      <x:c r="K3" s="1" t="s">
+      <x:c r="N3" s="1" t="s">
         <x:v>867</x:v>
       </x:c>
-      <x:c r="L3" s="1" t="s">
+      <x:c r="O3" s="1" t="s">
         <x:v>868</x:v>
       </x:c>
-      <x:c r="M3" s="1" t="s">
+      <x:c r="P3" s="1" t="s">
         <x:v>869</x:v>
-      </x:c>
-      <x:c r="N3" s="1" t="s">
-        <x:v>870</x:v>
-      </x:c>
-      <x:c r="O3" s="1" t="s">
-        <x:v>871</x:v>
-      </x:c>
-      <x:c r="P3" s="1" t="s">
-        <x:v>872</x:v>
       </x:c>
       <x:c r="Q3" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R3" s="1" t="s">
-        <x:v>873</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="S3" s="1" t="s">
-        <x:v>874</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="T3" s="1">
         <x:v>1</x:v>
@@ -16219,75 +16204,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA3" s="1" t="s">
-        <x:v>875</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="AB3" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC3" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="AD3" s="1" t="s">
-        <x:v>877</x:v>
+        <x:v>874</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="87.94999694824219" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>603</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>604</x:v>
-      </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
         <x:v>878</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>879</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
+      <x:c r="H4" s="1" t="s">
         <x:v>880</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="s">
+      <x:c r="I4" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="s">
         <x:v>881</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="s">
+      <x:c r="K4" s="1" t="s">
         <x:v>882</x:v>
       </x:c>
-      <x:c r="H4" s="1" t="s">
+      <x:c r="L4" s="1" t="s">
         <x:v>883</x:v>
       </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J4" s="1" t="s">
+      <x:c r="M4" s="1" t="s">
         <x:v>884</x:v>
       </x:c>
-      <x:c r="K4" s="1" t="s">
+      <x:c r="N4" s="1" t="s">
         <x:v>885</x:v>
       </x:c>
-      <x:c r="L4" s="1" t="s">
+      <x:c r="O4" s="1" t="s">
         <x:v>886</x:v>
       </x:c>
-      <x:c r="M4" s="1" t="s">
+      <x:c r="P4" s="1" t="s">
         <x:v>887</x:v>
       </x:c>
-      <x:c r="N4" s="1" t="s">
+      <x:c r="Q4" s="1" t="s">
         <x:v>888</x:v>
-      </x:c>
-      <x:c r="O4" s="1" t="s">
-        <x:v>889</x:v>
-      </x:c>
-      <x:c r="P4" s="1" t="s">
-        <x:v>890</x:v>
-      </x:c>
-      <x:c r="Q4" s="1" t="s">
-        <x:v>891</x:v>
       </x:c>
       <x:c r="R4" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="S4" s="1" t="s">
-        <x:v>892</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="T4" s="1">
         <x:v>2</x:v>
@@ -16311,66 +16296,66 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA4" s="1" t="s">
-        <x:v>893</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="AB4" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC4" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="AD4" s="1" t="s">
-        <x:v>895</x:v>
+        <x:v>892</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="87.94999694824219" customHeight="1">
       <x:c r="A5" s="1" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>615</x:v>
-      </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="s">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="G5" s="1" t="s">
         <x:v>896</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="H5" s="1" t="s">
         <x:v>897</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
+      <x:c r="I5" s="1" t="s">
         <x:v>898</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
+      <x:c r="J5" s="1" t="s">
         <x:v>899</x:v>
       </x:c>
-      <x:c r="H5" s="1" t="s">
+      <x:c r="K5" s="1" t="s">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="I5" s="1" t="s">
+      <x:c r="L5" s="1" t="s">
         <x:v>901</x:v>
       </x:c>
-      <x:c r="J5" s="1" t="s">
+      <x:c r="M5" s="1" t="s">
         <x:v>902</x:v>
       </x:c>
-      <x:c r="K5" s="1" t="s">
+      <x:c r="N5" s="1" t="s">
         <x:v>903</x:v>
       </x:c>
-      <x:c r="L5" s="1" t="s">
+      <x:c r="O5" s="1" t="s">
         <x:v>904</x:v>
       </x:c>
-      <x:c r="M5" s="1" t="s">
+      <x:c r="P5" s="1" t="s">
         <x:v>905</x:v>
-      </x:c>
-      <x:c r="N5" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O5" s="1" t="s">
-        <x:v>907</x:v>
-      </x:c>
-      <x:c r="P5" s="1" t="s">
-        <x:v>908</x:v>
       </x:c>
       <x:c r="Q5" s="1" t="s">
         <x:v>212</x:v>
@@ -16379,7 +16364,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S5" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="T5" s="1">
         <x:v>1</x:v>
@@ -16403,75 +16388,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA5" s="1" t="s">
-        <x:v>910</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="AB5" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC5" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="AD5" s="1" t="s">
-        <x:v>912</x:v>
+        <x:v>909</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="87.94999694824219" customHeight="1">
       <x:c r="A6" s="1" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>621</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>622</x:v>
-      </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
         <x:v>913</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="G6" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
         <x:v>914</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="I6" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="s">
         <x:v>915</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="s">
+      <x:c r="K6" s="1" t="s">
         <x:v>916</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>917</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J6" s="1" t="s">
-        <x:v>918</x:v>
-      </x:c>
-      <x:c r="K6" s="1" t="s">
-        <x:v>919</x:v>
-      </x:c>
       <x:c r="L6" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M6" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N6" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>921</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="P6" s="1" t="s">
-        <x:v>922</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="Q6" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R6" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="S6" s="1" t="s">
-        <x:v>924</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="T6" s="1">
         <x:v>2</x:v>
@@ -16495,66 +16480,66 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA6" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="AB6" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC6" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD6" s="1" t="s">
-        <x:v>926</x:v>
+        <x:v>923</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="87.94999694824219" customHeight="1">
       <x:c r="A7" s="1" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>631</x:v>
-      </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="s">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
         <x:v>927</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="I7" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J7" s="1" t="s">
         <x:v>928</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
+      <x:c r="K7" s="1" t="s">
         <x:v>929</x:v>
       </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J7" s="1" t="s">
-        <x:v>931</x:v>
-      </x:c>
-      <x:c r="K7" s="1" t="s">
-        <x:v>932</x:v>
-      </x:c>
       <x:c r="L7" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M7" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N7" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="P7" s="1" t="s">
-        <x:v>935</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="Q7" s="1" t="s">
         <x:v>212</x:v>
@@ -16563,7 +16548,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S7" s="1" t="s">
-        <x:v>936</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="T7" s="1">
         <x:v>1</x:v>
@@ -16587,66 +16572,66 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA7" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="AB7" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC7" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="AD7" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>936</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="87.94999694824219" customHeight="1">
       <x:c r="A8" s="1" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
         <x:v>637</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>638</x:v>
-      </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="G8" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H8" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I8" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J8" s="1" t="s">
         <x:v>940</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="K8" s="1" t="s">
         <x:v>941</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
+      <x:c r="L8" s="1" t="s">
         <x:v>942</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>943</x:v>
-      </x:c>
-      <x:c r="K8" s="1" t="s">
-        <x:v>944</x:v>
-      </x:c>
-      <x:c r="L8" s="1" t="s">
-        <x:v>945</x:v>
       </x:c>
       <x:c r="M8" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N8" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>946</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="P8" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q8" s="1" t="s">
         <x:v>212</x:v>
@@ -16655,7 +16640,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S8" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T8" s="1">
         <x:v>1</x:v>
@@ -16679,75 +16664,75 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA8" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="AB8" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC8" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="AD8" s="1" t="s">
-        <x:v>948</x:v>
+        <x:v>945</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="87.94999694824219" customHeight="1">
       <x:c r="A9" s="1" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>646</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="C9" s="1" t="s">
         <x:v>647</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>648</x:v>
-      </x:c>
       <x:c r="D9" s="1" t="s">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I9" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="s">
         <x:v>949</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="K9" s="1" t="s">
         <x:v>950</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>951</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="s">
-        <x:v>952</x:v>
-      </x:c>
-      <x:c r="K9" s="1" t="s">
-        <x:v>953</x:v>
-      </x:c>
       <x:c r="L9" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M9" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N9" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>954</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="P9" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q9" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R9" s="1" t="s">
-        <x:v>955</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="S9" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T9" s="1">
         <x:v>1</x:v>
@@ -16771,66 +16756,66 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA9" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="AB9" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC9" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="AD9" s="1" t="s">
-        <x:v>956</x:v>
+        <x:v>953</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="87.94999694824219" customHeight="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>652</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>653</x:v>
-      </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H10" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I10" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J10" s="1" t="s">
         <x:v>957</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="K10" s="1" t="s">
         <x:v>958</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>959</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J10" s="1" t="s">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c r="K10" s="1" t="s">
-        <x:v>961</x:v>
-      </x:c>
       <x:c r="L10" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M10" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N10" s="1" t="s">
-        <x:v>962</x:v>
+        <x:v>959</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>963</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="P10" s="1" t="s">
-        <x:v>964</x:v>
+        <x:v>961</x:v>
       </x:c>
       <x:c r="Q10" s="1" t="s">
         <x:v>212</x:v>
@@ -16839,7 +16824,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S10" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="T10" s="1">
         <x:v>1</x:v>
@@ -16863,75 +16848,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA10" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>963</x:v>
       </x:c>
       <x:c r="AB10" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC10" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD10" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>964</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="87.94999694824219" customHeight="1">
       <x:c r="A11" s="1" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>661</x:v>
-      </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>663</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
         <x:v>968</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
+      <x:c r="H11" s="1" t="s">
         <x:v>969</x:v>
       </x:c>
-      <x:c r="F11" s="1" t="s">
+      <x:c r="I11" s="1" t="s">
         <x:v>970</x:v>
       </x:c>
-      <x:c r="G11" s="1" t="s">
+      <x:c r="J11" s="1" t="s">
         <x:v>971</x:v>
       </x:c>
-      <x:c r="H11" s="1" t="s">
+      <x:c r="K11" s="1" t="s">
         <x:v>972</x:v>
       </x:c>
-      <x:c r="I11" s="1" t="s">
-        <x:v>973</x:v>
-      </x:c>
-      <x:c r="J11" s="1" t="s">
-        <x:v>974</x:v>
-      </x:c>
-      <x:c r="K11" s="1" t="s">
-        <x:v>975</x:v>
-      </x:c>
       <x:c r="L11" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M11" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N11" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>976</x:v>
+        <x:v>973</x:v>
       </x:c>
       <x:c r="P11" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="Q11" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R11" s="1" t="s">
-        <x:v>978</x:v>
+        <x:v>975</x:v>
       </x:c>
       <x:c r="S11" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T11" s="1">
         <x:v>1</x:v>
@@ -16955,75 +16940,75 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA11" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>976</x:v>
       </x:c>
       <x:c r="AB11" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC11" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="AD11" s="1" t="s">
-        <x:v>980</x:v>
+        <x:v>977</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="87.94999694824219" customHeight="1">
       <x:c r="A12" s="1" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
         <x:v>667</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>668</x:v>
-      </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>670</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>979</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H12" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I12" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J12" s="1" t="s">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="K12" s="1" t="s">
         <x:v>981</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
+      <x:c r="L12" s="1" t="s">
         <x:v>982</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J12" s="1" t="s">
-        <x:v>983</x:v>
-      </x:c>
-      <x:c r="K12" s="1" t="s">
-        <x:v>984</x:v>
-      </x:c>
-      <x:c r="L12" s="1" t="s">
-        <x:v>985</x:v>
       </x:c>
       <x:c r="M12" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N12" s="1" t="s">
-        <x:v>986</x:v>
+        <x:v>983</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="P12" s="1" t="s">
-        <x:v>988</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="Q12" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R12" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="S12" s="1" t="s">
-        <x:v>990</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="T12" s="1">
         <x:v>1</x:v>
@@ -17047,75 +17032,75 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA12" s="1" t="s">
-        <x:v>991</x:v>
+        <x:v>988</x:v>
       </x:c>
       <x:c r="AB12" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC12" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="AD12" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>989</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="87.94999694824219" customHeight="1">
       <x:c r="A13" s="1" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
         <x:v>675</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>676</x:v>
-      </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I13" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="K13" s="1" t="s">
         <x:v>993</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
+      <x:c r="L13" s="1" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="M13" s="1" t="s">
         <x:v>994</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
+      <x:c r="N13" s="1" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="O13" s="1" t="s">
         <x:v>995</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
-        <x:v>952</x:v>
-      </x:c>
-      <x:c r="K13" s="1" t="s">
-        <x:v>996</x:v>
-      </x:c>
-      <x:c r="L13" s="1" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="M13" s="1" t="s">
-        <x:v>997</x:v>
-      </x:c>
-      <x:c r="N13" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O13" s="1" t="s">
-        <x:v>998</x:v>
-      </x:c>
       <x:c r="P13" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q13" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R13" s="1" t="s">
-        <x:v>999</x:v>
+        <x:v>996</x:v>
       </x:c>
       <x:c r="S13" s="1" t="s">
-        <x:v>1000</x:v>
+        <x:v>997</x:v>
       </x:c>
       <x:c r="T13" s="1">
         <x:v>1</x:v>
@@ -17139,75 +17124,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA13" s="1" t="s">
-        <x:v>1001</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="AB13" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC13" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="AD13" s="1" t="s">
-        <x:v>1002</x:v>
+        <x:v>999</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="87.94999694824219" customHeight="1">
       <x:c r="A14" s="1" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
         <x:v>682</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>683</x:v>
-      </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H14" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I14" s="1" t="s">
         <x:v>1004</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="J14" s="1" t="s">
         <x:v>1005</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="s">
+      <x:c r="K14" s="1" t="s">
         <x:v>1006</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="s">
-        <x:v>1007</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
-        <x:v>1008</x:v>
-      </x:c>
-      <x:c r="K14" s="1" t="s">
-        <x:v>1009</x:v>
-      </x:c>
       <x:c r="L14" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M14" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N14" s="1" t="s">
-        <x:v>1010</x:v>
+        <x:v>1007</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
-        <x:v>1011</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="P14" s="1" t="s">
-        <x:v>1012</x:v>
+        <x:v>1009</x:v>
       </x:c>
       <x:c r="Q14" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R14" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="S14" s="1" t="s">
-        <x:v>1014</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="T14" s="1">
         <x:v>2</x:v>
@@ -17231,75 +17216,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA14" s="1" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="AB14" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AC14" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="AD14" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1013</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="87.94999694824219" customHeight="1">
       <x:c r="A15" s="1" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>689</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>690</x:v>
-      </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>692</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="D15" s="1" t="str">
         <x:v>Peer-reviewed conference publication (USENIX Security 2026; formal proceedings, pp. 1827--1845) + arXiv preprint</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H15" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I15" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="K15" s="1" t="s">
         <x:v>1017</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>1018</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
-        <x:v>1019</x:v>
-      </x:c>
-      <x:c r="K15" s="1" t="s">
-        <x:v>1020</x:v>
-      </x:c>
       <x:c r="L15" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M15" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N15" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>1021</x:v>
+        <x:v>1018</x:v>
       </x:c>
       <x:c r="P15" s="1" t="s">
-        <x:v>1022</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="Q15" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R15" s="1" t="s">
-        <x:v>1023</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="S15" s="1" t="s">
-        <x:v>1024</x:v>
+        <x:v>1021</x:v>
       </x:c>
       <x:c r="T15" s="1">
         <x:v>2</x:v>
@@ -17323,75 +17308,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA15" s="1" t="s">
-        <x:v>1025</x:v>
+        <x:v>1022</x:v>
       </x:c>
       <x:c r="AB15" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AC15" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD15" s="1" t="s">
-        <x:v>1026</x:v>
+        <x:v>1023</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="87.94999694824219" customHeight="1">
       <x:c r="A16" s="1" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
         <x:v>696</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="C16" s="1" t="s">
         <x:v>697</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>698</x:v>
-      </x:c>
       <x:c r="D16" s="1" t="s">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H16" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I16" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
         <x:v>1027</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="K16" s="1" t="s">
         <x:v>1028</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>1029</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
-        <x:v>1030</x:v>
-      </x:c>
-      <x:c r="K16" s="1" t="s">
-        <x:v>1031</x:v>
-      </x:c>
       <x:c r="L16" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M16" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N16" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>1032</x:v>
+        <x:v>1029</x:v>
       </x:c>
       <x:c r="P16" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q16" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R16" s="1" t="s">
-        <x:v>1033</x:v>
+        <x:v>1030</x:v>
       </x:c>
       <x:c r="S16" s="1" t="s">
-        <x:v>1034</x:v>
+        <x:v>1031</x:v>
       </x:c>
       <x:c r="T16" s="1">
         <x:v>2</x:v>
@@ -17415,66 +17400,66 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA16" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>1032</x:v>
       </x:c>
       <x:c r="AB16" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC16" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="AD16" s="1" t="s">
-        <x:v>1036</x:v>
+        <x:v>1033</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="87.94999694824219" customHeight="1">
       <x:c r="A17" s="1" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
         <x:v>701</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="C17" s="1" t="s">
         <x:v>702</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>703</x:v>
-      </x:c>
       <x:c r="D17" s="1" t="s">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H17" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="K17" s="1" t="s">
         <x:v>1037</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
+      <x:c r="L17" s="1" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="M17" s="1" t="s">
         <x:v>1038</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
+      <x:c r="N17" s="1" t="s">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H17" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
-        <x:v>952</x:v>
-      </x:c>
-      <x:c r="K17" s="1" t="s">
+      <x:c r="O17" s="1" t="s">
         <x:v>1040</x:v>
       </x:c>
-      <x:c r="L17" s="1" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="M17" s="1" t="s">
-        <x:v>1041</x:v>
-      </x:c>
-      <x:c r="N17" s="1" t="s">
-        <x:v>1042</x:v>
-      </x:c>
-      <x:c r="O17" s="1" t="s">
-        <x:v>1043</x:v>
-      </x:c>
       <x:c r="P17" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q17" s="1" t="s">
         <x:v>212</x:v>
@@ -17483,7 +17468,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S17" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="T17" s="1">
         <x:v>2</x:v>
@@ -17507,66 +17492,66 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA17" s="1" t="s">
-        <x:v>1044</x:v>
+        <x:v>1041</x:v>
       </x:c>
       <x:c r="AB17" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AC17" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="AD17" s="1" t="s">
-        <x:v>1045</x:v>
+        <x:v>1042</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="87.94999694824219" customHeight="1">
       <x:c r="A18" s="1" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
         <x:v>707</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>708</x:v>
-      </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I18" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="s">
         <x:v>1046</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="K18" s="1" t="s">
         <x:v>1047</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>1048</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I18" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J18" s="1" t="s">
-        <x:v>1049</x:v>
-      </x:c>
-      <x:c r="K18" s="1" t="s">
-        <x:v>1050</x:v>
-      </x:c>
       <x:c r="L18" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M18" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N18" s="1" t="s">
-        <x:v>1051</x:v>
+        <x:v>1048</x:v>
       </x:c>
       <x:c r="O18" s="1" t="s">
-        <x:v>1052</x:v>
+        <x:v>1049</x:v>
       </x:c>
       <x:c r="P18" s="1" t="s">
-        <x:v>1053</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="Q18" s="1" t="s">
         <x:v>212</x:v>
@@ -17575,7 +17560,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S18" s="1" t="s">
-        <x:v>1054</x:v>
+        <x:v>1051</x:v>
       </x:c>
       <x:c r="T18" s="1">
         <x:v>1</x:v>
@@ -17599,75 +17584,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA18" s="1" t="s">
-        <x:v>1055</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="AB18" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AC18" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD18" s="1" t="s">
-        <x:v>1056</x:v>
+        <x:v>1053</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="87.94999694824219" customHeight="1">
       <x:c r="A19" s="1" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
         <x:v>715</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="C19" s="1" t="s">
         <x:v>716</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>717</x:v>
-      </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1057</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>1058</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
-        <x:v>847</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>952</x:v>
+        <x:v>949</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>1059</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="L19" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M19" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N19" s="1" t="s">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="O19" s="1" t="s">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="P19" s="1" t="s">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="Q19" s="1" t="s">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="R19" s="1" t="s">
         <x:v>1060</x:v>
       </x:c>
-      <x:c r="O19" s="1" t="s">
-        <x:v>1061</x:v>
-      </x:c>
-      <x:c r="P19" s="1" t="s">
-        <x:v>947</x:v>
-      </x:c>
-      <x:c r="Q19" s="1" t="s">
-        <x:v>1062</x:v>
-      </x:c>
-      <x:c r="R19" s="1" t="s">
-        <x:v>1063</x:v>
-      </x:c>
       <x:c r="S19" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T19" s="1">
         <x:v>2</x:v>
@@ -17691,75 +17676,75 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA19" s="1" t="s">
-        <x:v>1064</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="AB19" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC19" s="1" t="s">
-        <x:v>1065</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="AD19" s="1" t="s">
-        <x:v>1066</x:v>
+        <x:v>1063</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="87.94999694824219" customHeight="1">
       <x:c r="A20" s="1" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
         <x:v>722</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>723</x:v>
-      </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H20" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I20" s="1" t="s">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="J20" s="1" t="s">
         <x:v>1067</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="K20" s="1" t="s">
         <x:v>1068</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>1069</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I20" s="1" t="s">
-        <x:v>901</x:v>
-      </x:c>
-      <x:c r="J20" s="1" t="s">
-        <x:v>1070</x:v>
-      </x:c>
-      <x:c r="K20" s="1" t="s">
-        <x:v>1071</x:v>
-      </x:c>
       <x:c r="L20" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M20" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N20" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="O20" s="1" t="s">
-        <x:v>1072</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="P20" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q20" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R20" s="1" t="s">
-        <x:v>1073</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="S20" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T20" s="1">
         <x:v>1</x:v>
@@ -17783,63 +17768,63 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA20" s="1" t="s">
-        <x:v>1074</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="AB20" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC20" s="1" t="s">
-        <x:v>1075</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="AD20" s="1" t="s">
-        <x:v>1076</x:v>
+        <x:v>1073</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="87.94999694824219" customHeight="1">
       <x:c r="A21" s="1" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
         <x:v>727</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>728</x:v>
-      </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>1077</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>1078</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>1079</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>1080</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>1007</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>1081</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="K21" s="1" t="s">
-        <x:v>1082</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="L21" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M21" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N21" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O21" s="1" t="s">
-        <x:v>1083</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="P21" s="1" t="s">
         <x:v>212</x:v>
@@ -17851,7 +17836,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S21" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T21" s="1">
         <x:v>1</x:v>
@@ -17875,66 +17860,66 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA21" s="1" t="s">
-        <x:v>1084</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="AB21" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AC21" s="1" t="s">
-        <x:v>1085</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="AD21" s="1" t="s">
-        <x:v>1086</x:v>
+        <x:v>1083</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="87.94999694824219" customHeight="1">
       <x:c r="A22" s="1" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
         <x:v>734</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>735</x:v>
-      </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>737</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H22" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I22" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="K22" s="1" t="s">
         <x:v>1087</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>1088</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>1089</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
-        <x:v>952</x:v>
-      </x:c>
-      <x:c r="K22" s="1" t="s">
-        <x:v>1090</x:v>
-      </x:c>
       <x:c r="L22" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M22" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N22" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="O22" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="P22" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q22" s="1" t="s">
         <x:v>212</x:v>
@@ -17943,7 +17928,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S22" s="1" t="s">
-        <x:v>1092</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="T22" s="1">
         <x:v>2</x:v>
@@ -17967,75 +17952,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA22" s="1" t="s">
-        <x:v>1093</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="AB22" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC22" s="1" t="s">
-        <x:v>1094</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="AD22" s="1" t="s">
-        <x:v>1095</x:v>
+        <x:v>1092</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="87.94999694824219" customHeight="1">
       <x:c r="A23" s="1" t="s">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
         <x:v>740</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="C23" s="1" t="s">
         <x:v>741</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>743</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="D23" s="1" t="str">
+        <x:v>Peer-reviewed conference paper (ICSE 2026; DOI 10.1145/3744916.3773113)</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I23" s="1" t="s">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
         <x:v>1096</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
+      <x:c r="K23" s="1" t="s">
         <x:v>1097</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="s">
+      <x:c r="L23" s="1" t="s">
         <x:v>1098</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>1099</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I23" s="1" t="s">
-        <x:v>973</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
-        <x:v>1100</x:v>
-      </x:c>
-      <x:c r="K23" s="1" t="s">
-        <x:v>1101</x:v>
-      </x:c>
-      <x:c r="L23" s="1" t="s">
-        <x:v>1102</x:v>
       </x:c>
       <x:c r="M23" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N23" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O23" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="P23" s="1" t="s">
-        <x:v>1104</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="Q23" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R23" s="1" t="s">
-        <x:v>1105</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="S23" s="1" t="s">
-        <x:v>1106</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="T23" s="1">
         <x:v>2</x:v>
@@ -18059,75 +18044,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA23" s="1" t="s">
-        <x:v>1107</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="AB23" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC23" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="AD23" s="1" t="s">
-        <x:v>1108</x:v>
+        <x:v>1104</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="87.94999694824219" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>748</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="H24" s="1" t="s">
         <x:v>1109</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="I24" s="1" t="s">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
         <x:v>1110</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>1038</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
+      <x:c r="K24" s="1" t="s">
         <x:v>1111</x:v>
       </x:c>
-      <x:c r="G24" s="1" t="s">
-        <x:v>1112</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>1113</x:v>
-      </x:c>
-      <x:c r="I24" s="1" t="s">
-        <x:v>901</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
-        <x:v>1114</x:v>
-      </x:c>
-      <x:c r="K24" s="1" t="s">
-        <x:v>1115</x:v>
-      </x:c>
       <x:c r="L24" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M24" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N24" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="O24" s="1" t="s">
-        <x:v>1116</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="P24" s="1" t="s">
-        <x:v>1117</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="Q24" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R24" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="S24" s="1" t="s">
-        <x:v>1119</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="T24" s="1">
         <x:v>2</x:v>
@@ -18151,66 +18136,66 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA24" s="1" t="s">
-        <x:v>1120</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="AB24" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC24" s="1" t="s">
-        <x:v>1121</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="AD24" s="1" t="s">
-        <x:v>1122</x:v>
+        <x:v>1118</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="87.94999694824219" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>754</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>1123</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="H25" s="1" t="s">
         <x:v>1124</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
+      <x:c r="I25" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
         <x:v>1125</x:v>
       </x:c>
-      <x:c r="F25" s="1" t="s">
+      <x:c r="K25" s="1" t="s">
         <x:v>1126</x:v>
       </x:c>
-      <x:c r="G25" s="1" t="s">
+      <x:c r="L25" s="1" t="s">
         <x:v>1127</x:v>
       </x:c>
-      <x:c r="H25" s="1" t="s">
+      <x:c r="M25" s="1" t="s">
         <x:v>1128</x:v>
       </x:c>
-      <x:c r="I25" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
+      <x:c r="N25" s="1" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="O25" s="1" t="s">
         <x:v>1129</x:v>
       </x:c>
-      <x:c r="K25" s="1" t="s">
+      <x:c r="P25" s="1" t="s">
         <x:v>1130</x:v>
-      </x:c>
-      <x:c r="L25" s="1" t="s">
-        <x:v>1131</x:v>
-      </x:c>
-      <x:c r="M25" s="1" t="s">
-        <x:v>1132</x:v>
-      </x:c>
-      <x:c r="N25" s="1" t="s">
-        <x:v>962</x:v>
-      </x:c>
-      <x:c r="O25" s="1" t="s">
-        <x:v>1133</x:v>
-      </x:c>
-      <x:c r="P25" s="1" t="s">
-        <x:v>1134</x:v>
       </x:c>
       <x:c r="Q25" s="1" t="s">
         <x:v>212</x:v>
@@ -18219,7 +18204,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S25" s="1" t="s">
-        <x:v>1135</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="T25" s="1">
         <x:v>2</x:v>
@@ -18243,75 +18228,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA25" s="1" t="s">
-        <x:v>1136</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="AB25" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC25" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD25" s="1" t="s">
-        <x:v>1137</x:v>
+        <x:v>1133</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="87.94999694824219" customHeight="1">
       <x:c r="A26" s="1" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>760</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>761</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>763</x:v>
-      </x:c>
       <x:c r="D26" s="1" t="s">
+        <x:v>1134</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>1136</x:v>
+      </x:c>
+      <x:c r="H26" s="1" t="s">
+        <x:v>1137</x:v>
+      </x:c>
+      <x:c r="I26" s="1" t="s">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>1138</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
+      <x:c r="K26" s="1" t="s">
         <x:v>1139</x:v>
       </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>1140</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="s">
-        <x:v>1141</x:v>
-      </x:c>
-      <x:c r="I26" s="1" t="s">
-        <x:v>1007</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
-        <x:v>1142</x:v>
-      </x:c>
-      <x:c r="K26" s="1" t="s">
-        <x:v>1143</x:v>
-      </x:c>
       <x:c r="L26" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M26" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N26" s="1" t="s">
-        <x:v>962</x:v>
+        <x:v>959</x:v>
       </x:c>
       <x:c r="O26" s="1" t="s">
-        <x:v>1144</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="P26" s="1" t="s">
-        <x:v>1145</x:v>
+        <x:v>1141</x:v>
       </x:c>
       <x:c r="Q26" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R26" s="1" t="s">
-        <x:v>1146</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="S26" s="1" t="s">
-        <x:v>1147</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="T26" s="1">
         <x:v>1</x:v>
@@ -18335,75 +18320,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA26" s="1" t="s">
-        <x:v>1148</x:v>
+        <x:v>1144</x:v>
       </x:c>
       <x:c r="AB26" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC26" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="AD26" s="1" t="s">
-        <x:v>1149</x:v>
+        <x:v>1145</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="87.94999694824219" customHeight="1">
       <x:c r="A27" s="1" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>769</x:v>
       </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>770</x:v>
-      </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>772</x:v>
-      </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>1150</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>1151</x:v>
+        <x:v>1147</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="I27" s="1" t="s">
-        <x:v>1007</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>1152</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="K27" s="1" t="s">
-        <x:v>1153</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="L27" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M27" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N27" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="O27" s="1" t="s">
-        <x:v>1154</x:v>
+        <x:v>1150</x:v>
       </x:c>
       <x:c r="P27" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q27" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R27" s="1" t="s">
-        <x:v>1155</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="S27" s="1" t="s">
-        <x:v>1156</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="T27" s="1">
         <x:v>1</x:v>
@@ -18427,75 +18412,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA27" s="1" t="s">
-        <x:v>1157</x:v>
+        <x:v>1153</x:v>
       </x:c>
       <x:c r="AB27" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AC27" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="AD27" s="1" t="s">
-        <x:v>1158</x:v>
+        <x:v>1154</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="87.94999694824219" customHeight="1">
       <x:c r="A28" s="1" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>773</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>775</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>778</x:v>
-      </x:c>
       <x:c r="D28" s="1" t="s">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>1156</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I28" s="1" t="s">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="K28" s="1" t="s">
+        <x:v>1158</x:v>
+      </x:c>
+      <x:c r="L28" s="1" t="s">
         <x:v>1159</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>843</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
+      <x:c r="M28" s="1" t="s">
         <x:v>1160</x:v>
       </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I28" s="1" t="s">
-        <x:v>847</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
+      <x:c r="N28" s="1" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="O28" s="1" t="s">
         <x:v>1161</x:v>
       </x:c>
-      <x:c r="K28" s="1" t="s">
+      <x:c r="P28" s="1" t="s">
         <x:v>1162</x:v>
       </x:c>
-      <x:c r="L28" s="1" t="s">
+      <x:c r="Q28" s="1" t="s">
         <x:v>1163</x:v>
       </x:c>
-      <x:c r="M28" s="1" t="s">
+      <x:c r="R28" s="1" t="s">
         <x:v>1164</x:v>
       </x:c>
-      <x:c r="N28" s="1" t="s">
-        <x:v>962</x:v>
-      </x:c>
-      <x:c r="O28" s="1" t="s">
+      <x:c r="S28" s="1" t="s">
         <x:v>1165</x:v>
-      </x:c>
-      <x:c r="P28" s="1" t="s">
-        <x:v>1166</x:v>
-      </x:c>
-      <x:c r="Q28" s="1" t="s">
-        <x:v>1167</x:v>
-      </x:c>
-      <x:c r="R28" s="1" t="s">
-        <x:v>1168</x:v>
-      </x:c>
-      <x:c r="S28" s="1" t="s">
-        <x:v>1169</x:v>
       </x:c>
       <x:c r="T28" s="1">
         <x:v>1</x:v>
@@ -18519,66 +18504,66 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA28" s="1" t="s">
-        <x:v>1170</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="AB28" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AC28" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="AD28" s="1" t="s">
-        <x:v>1171</x:v>
+        <x:v>1167</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="87.94999694824219" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>1172</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>1173</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>847</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>1174</x:v>
+        <x:v>1170</x:v>
       </x:c>
       <x:c r="K29" s="1" t="s">
-        <x:v>1175</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="L29" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M29" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="N29" s="1" t="s">
-        <x:v>1060</x:v>
+        <x:v>1057</x:v>
       </x:c>
       <x:c r="O29" s="1" t="s">
-        <x:v>1176</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="P29" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="Q29" s="1" t="s">
         <x:v>212</x:v>
@@ -18587,7 +18572,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="S29" s="1" t="s">
-        <x:v>1177</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="T29" s="1">
         <x:v>1</x:v>
@@ -18611,75 +18596,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA29" s="1" t="s">
-        <x:v>1178</x:v>
+        <x:v>1174</x:v>
       </x:c>
       <x:c r="AB29" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC29" s="1" t="s">
-        <x:v>1094</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="AD29" s="1" t="s">
-        <x:v>1179</x:v>
+        <x:v>1175</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="87.94999694824219" customHeight="1">
       <x:c r="A30" s="1" t="s">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>789</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>790</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>792</x:v>
-      </x:c>
       <x:c r="D30" s="1" t="s">
+        <x:v>1176</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>1177</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>1178</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>1179</x:v>
+      </x:c>
+      <x:c r="I30" s="1" t="s">
         <x:v>1180</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>1088</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
+      <x:c r="J30" s="1" t="s">
         <x:v>1181</x:v>
       </x:c>
-      <x:c r="G30" s="1" t="s">
+      <x:c r="K30" s="1" t="s">
         <x:v>1182</x:v>
       </x:c>
-      <x:c r="H30" s="1" t="s">
-        <x:v>1183</x:v>
-      </x:c>
-      <x:c r="I30" s="1" t="s">
-        <x:v>1184</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
-        <x:v>1185</x:v>
-      </x:c>
-      <x:c r="K30" s="1" t="s">
-        <x:v>1186</x:v>
-      </x:c>
       <x:c r="L30" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="M30" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="N30" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O30" s="1" t="s">
-        <x:v>1187</x:v>
+      <x:c r="N30" s="1" t="str">
+        <x:v>Component; configuration</x:v>
+      </x:c>
+      <x:c r="O30" s="1" t="str">
+        <x:v>A three-backbone comparison fixes the pipeline, hyperparameters, prompts, and orchestration while substituting DeepSeek-V4-Flash, GPT-5.4-mini, and Qwen-3.6-Flash; it isolates backbone choice within a retained LLM-mediated component, not LLM presence or coordination. Four component-level ablations remove malicious-shell-command detection, enrichment, dynamic augmentation, or self-consistency. Reported relative F1 changes are -7.85%, -0.30%, -3.87%, and -4.49%, respectively; the corresponding absolute drops reported in the review are 7.7 points for shell-command detection and 4.4 points for self-consistency. The design is non-factorial, and agent coordination is not isolated.</x:v>
       </x:c>
       <x:c r="P30" s="1" t="s">
-        <x:v>1188</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="Q30" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R30" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="S30" s="1" t="s">
-        <x:v>1190</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="T30" s="1">
         <x:v>2</x:v>
@@ -18703,75 +18688,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA30" s="1" t="s">
-        <x:v>1191</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="AB30" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AC30" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="AD30" s="1" t="s">
-        <x:v>1192</x:v>
+        <x:v>1187</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="87.94999694824219" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>1189</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>1190</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>1191</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="s">
+        <x:v>1192</x:v>
+      </x:c>
+      <x:c r="I31" s="1" t="s">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
         <x:v>1193</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
+      <x:c r="K31" s="1" t="s">
         <x:v>1194</x:v>
       </x:c>
-      <x:c r="F31" s="1" t="s">
+      <x:c r="L31" s="1" t="s">
         <x:v>1195</x:v>
       </x:c>
-      <x:c r="G31" s="1" t="s">
+      <x:c r="M31" s="1" t="s">
         <x:v>1196</x:v>
       </x:c>
-      <x:c r="H31" s="1" t="s">
+      <x:c r="N31" s="1" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="O31" s="1" t="s">
         <x:v>1197</x:v>
       </x:c>
-      <x:c r="I31" s="1" t="s">
-        <x:v>973</x:v>
-      </x:c>
-      <x:c r="J31" s="1" t="s">
+      <x:c r="P31" s="1" t="s">
         <x:v>1198</x:v>
-      </x:c>
-      <x:c r="K31" s="1" t="s">
-        <x:v>1199</x:v>
-      </x:c>
-      <x:c r="L31" s="1" t="s">
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="M31" s="1" t="s">
-        <x:v>1201</x:v>
-      </x:c>
-      <x:c r="N31" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O31" s="1" t="s">
-        <x:v>1202</x:v>
-      </x:c>
-      <x:c r="P31" s="1" t="s">
-        <x:v>1203</x:v>
       </x:c>
       <x:c r="Q31" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
       <x:c r="R31" s="1" t="s">
-        <x:v>1204</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="S31" s="1" t="s">
-        <x:v>1205</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="T31" s="1">
         <x:v>2</x:v>
@@ -18795,75 +18780,75 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA31" s="1" t="s">
-        <x:v>1206</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="AB31" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="AC31" s="1" t="s">
-        <x:v>1207</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="AD31" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1203</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="87.94999694824219" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
+        <x:v>1204</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>1205</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>1207</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="s">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="I32" s="1" t="s">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="K32" s="1" t="s">
         <x:v>1209</x:v>
       </x:c>
-      <x:c r="E32" s="1" t="s">
+      <x:c r="L32" s="1" t="s">
         <x:v>1210</x:v>
       </x:c>
-      <x:c r="F32" s="1" t="s">
+      <x:c r="M32" s="1" t="s">
         <x:v>1211</x:v>
       </x:c>
-      <x:c r="G32" s="1" t="s">
+      <x:c r="N32" s="1" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="O32" s="1" t="s">
         <x:v>1212</x:v>
       </x:c>
-      <x:c r="H32" s="1" t="s">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="I32" s="1" t="s">
-        <x:v>1007</x:v>
-      </x:c>
-      <x:c r="J32" s="1" t="s">
+      <x:c r="P32" s="1" t="s">
         <x:v>1213</x:v>
       </x:c>
-      <x:c r="K32" s="1" t="s">
+      <x:c r="Q32" s="1" t="s">
         <x:v>1214</x:v>
       </x:c>
-      <x:c r="L32" s="1" t="s">
+      <x:c r="R32" s="1" t="s">
         <x:v>1215</x:v>
       </x:c>
-      <x:c r="M32" s="1" t="s">
+      <x:c r="S32" s="1" t="s">
         <x:v>1216</x:v>
-      </x:c>
-      <x:c r="N32" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O32" s="1" t="s">
-        <x:v>1217</x:v>
-      </x:c>
-      <x:c r="P32" s="1" t="s">
-        <x:v>1218</x:v>
-      </x:c>
-      <x:c r="Q32" s="1" t="s">
-        <x:v>1219</x:v>
-      </x:c>
-      <x:c r="R32" s="1" t="s">
-        <x:v>1220</x:v>
-      </x:c>
-      <x:c r="S32" s="1" t="s">
-        <x:v>1221</x:v>
       </x:c>
       <x:c r="T32" s="1">
         <x:v>2</x:v>
@@ -18887,75 +18872,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA32" s="1" t="s">
-        <x:v>1222</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="AB32" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AC32" s="1" t="s">
-        <x:v>1223</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="AD32" s="1" t="s">
-        <x:v>1224</x:v>
+        <x:v>1219</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="87.94999694824219" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
+        <x:v>1220</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>1221</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>1222</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>1223</x:v>
+      </x:c>
+      <x:c r="H33" s="1" t="s">
+        <x:v>1224</x:v>
+      </x:c>
+      <x:c r="I33" s="1" t="s">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
         <x:v>1225</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
+      <x:c r="K33" s="1" t="s">
         <x:v>1226</x:v>
       </x:c>
-      <x:c r="F33" s="1" t="s">
+      <x:c r="L33" s="1" t="s">
         <x:v>1227</x:v>
       </x:c>
-      <x:c r="G33" s="1" t="s">
+      <x:c r="M33" s="1" t="s">
         <x:v>1228</x:v>
       </x:c>
-      <x:c r="H33" s="1" t="s">
+      <x:c r="N33" s="1" t="s">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="O33" s="1" t="s">
         <x:v>1229</x:v>
       </x:c>
-      <x:c r="I33" s="1" t="s">
-        <x:v>1007</x:v>
-      </x:c>
-      <x:c r="J33" s="1" t="s">
+      <x:c r="P33" s="1" t="s">
         <x:v>1230</x:v>
       </x:c>
-      <x:c r="K33" s="1" t="s">
+      <x:c r="Q33" s="1" t="s">
         <x:v>1231</x:v>
       </x:c>
-      <x:c r="L33" s="1" t="s">
+      <x:c r="R33" s="1" t="s">
         <x:v>1232</x:v>
       </x:c>
-      <x:c r="M33" s="1" t="s">
+      <x:c r="S33" s="1" t="s">
         <x:v>1233</x:v>
-      </x:c>
-      <x:c r="N33" s="1" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="O33" s="1" t="s">
-        <x:v>1234</x:v>
-      </x:c>
-      <x:c r="P33" s="1" t="s">
-        <x:v>1235</x:v>
-      </x:c>
-      <x:c r="Q33" s="1" t="s">
-        <x:v>1236</x:v>
-      </x:c>
-      <x:c r="R33" s="1" t="s">
-        <x:v>1237</x:v>
-      </x:c>
-      <x:c r="S33" s="1" t="s">
-        <x:v>1238</x:v>
       </x:c>
       <x:c r="T33" s="1">
         <x:v>2</x:v>
@@ -18979,16 +18964,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AA33" s="1" t="s">
-        <x:v>1239</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="AB33" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="AC33" s="1" t="s">
-        <x:v>1240</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="AD33" s="1" t="s">
-        <x:v>1241</x:v>
+        <x:v>1236</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19095,10 +19080,10 @@
         <x:v>Component isolation</x:v>
       </x:c>
       <x:c r="B7" s="1" t="str">
-        <x:v>Attribution of LLM-related components within the stated role and task</x:v>
+        <x:v>Attribution of the focal LLM-mediated component within the stated role and task</x:v>
       </x:c>
       <x:c r="C7" s="1" t="str">
-        <x:v>2=orthogonal; 1=component/architecture comparison with residual confounding; 0=None/NR</x:v>
+        <x:v>2=matched addition/removal or functionally comparable replacement with evaluation data and non-target pipeline fixed; 1=within-component configuration comparison or component/architecture comparison with residual confounding; 0=None/NR</x:v>
       </x:c>
       <x:c r="D7" s="1" t="str">
         <x:v>ablation_type; ablation_detail</x:v>
@@ -19134,72 +19119,72 @@
   <x:sheetData>
     <x:row r="1" ht="32.099998474121094" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>1242</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>1243</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>1244</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>1245</x:v>
+        <x:v>1240</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="75.94999694824219" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1246</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>1247</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>1248</x:v>
+        <x:v>1243</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="75.94999694824219" customHeight="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>1249</x:v>
+        <x:v>1244</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>1250</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>1251</x:v>
+        <x:v>1246</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="75.94999694824219" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>1252</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>1253</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>1254</x:v>
+        <x:v>1249</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="75.94999694824219" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>1255</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>1256</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>1257</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>1258</x:v>
+        <x:v>1253</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19384,7 +19369,7 @@
         <x:v>Direct role-specific corpus audit</x:v>
       </x:c>
       <x:c r="E4" s="1" t="str">
-        <x:v>Across 14 primary Constructor studies, 4 have component-isolation score 0, 9 score 1, and S_MALGUARD_USENIX alone scores 2. Its orthogonal comparison evaluates raw top-centrality APIs against GPT-3.5-filtered APIs. The remaining component comparisons retain representation, artifact, pipeline-stage, data, or budget confounding.</x:v>
+        <x:v>Across 14 primary Constructor studies, 4 have component-isolation score 0, 9 score 1, and S_MALGUARD_USENIX alone scores 2. Its orthogonal comparison evaluates raw top-centrality APIs against GPT-3.5-filtered APIs while holding the downstream classifiers and evaluation fixed. The other component comparisons either vary configurations within a retained component or do not hold the input data, artifact type or interface, downstream training and evaluation, and other non-target pipeline elements fixed.</x:v>
       </x:c>
       <x:c r="F4" s="1" t="str">
         <x:v>S_MALGUARD_USENIX provides the sole orthogonal comparison and therefore precludes an absolute claim that no Constructor component is isolated.</x:v>
@@ -19394,7 +19379,7 @@
       </x:c>
       <x:c r="H4" s="1"/>
       <x:c r="I4" s="1" t="str">
-        <x:v>Component removal can change representation, information budget, rule content, downstream capacity, or construction–evaluation overlap.</x:v>
+        <x:v>A fair constructor comparison must hold the input data, artifact type or interface, downstream training and evaluation, and other non-target pipeline elements fixed. Differences in generated content are part of the intervention; differences in information budget, downstream capacity, or construction–evaluation overlap can still confound attribution.</x:v>
       </x:c>
       <x:c r="J4" s="1" t="str">
         <x:v>Some task-specific component effects are supported, but the evidence does not identify a general LLM-constructor advantage.</x:v>
